--- a/Templates/IndividualPlanTemplate.xlsx
+++ b/Templates/IndividualPlanTemplate.xlsx
@@ -258,9 +258,6 @@
     <t>примечание</t>
   </si>
   <si>
-    <t>СВОБОДНАЯ ТАБЛИЦА</t>
-  </si>
-  <si>
     <t>Форма повышения квалификации преподавателя</t>
   </si>
   <si>
@@ -929,6 +926,9 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+  </si>
+  <si>
+    <t>СВОДНАЯ ТАБЛИЦА</t>
   </si>
 </sst>
 </file>
@@ -1388,32 +1388,77 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1424,50 +1469,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1478,14 +1499,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1496,24 +1514,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1577,6 +1577,15 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1586,62 +1595,92 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1652,9 +1691,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1663,42 +1699,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2006,7 +2006,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2021,60 +2021,60 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1"/>
     <row r="6" spans="1:10" ht="30" customHeight="1"/>
@@ -2082,193 +2082,208 @@
     <row r="8" spans="1:10" ht="30" customHeight="1"/>
     <row r="9" spans="1:10" ht="30" customHeight="1"/>
     <row r="10" spans="1:10" ht="39.6" customHeight="1">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
     </row>
     <row r="11" spans="1:10" ht="40.200000000000003" customHeight="1">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
     </row>
     <row r="12" spans="1:10" ht="40.200000000000003" customHeight="1">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="76"/>
     </row>
     <row r="13" spans="1:10" ht="28.95" customHeight="1"/>
     <row r="14" spans="1:10" ht="34.200000000000003" customHeight="1"/>
     <row r="15" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="71" t="s">
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
     </row>
     <row r="16" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="72" t="s">
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="78" t="s">
+        <v>268</v>
+      </c>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.2" customHeight="1">
+      <c r="A17" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="71" t="s">
         <v>269</v>
       </c>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="73" t="s">
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+    </row>
+    <row r="18" spans="1:10" ht="25.2" customHeight="1">
+      <c r="A18" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="71" t="s">
         <v>270</v>
       </c>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-    </row>
-    <row r="18" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A18" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="73" t="s">
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+    </row>
+    <row r="19" spans="1:10" ht="25.2" customHeight="1">
+      <c r="A19" s="72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="70" t="s">
         <v>271</v>
       </c>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
-    </row>
-    <row r="19" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A19" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="78" t="s">
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+    </row>
+    <row r="20" spans="1:10" ht="25.2" customHeight="1">
+      <c r="A20" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="71" t="s">
         <v>272</v>
       </c>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-    </row>
-    <row r="20" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A20" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="73" t="s">
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+    </row>
+    <row r="21" spans="1:10" ht="25.2" customHeight="1">
+      <c r="A21" s="72" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="70">
+        <v>1994</v>
+      </c>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+    </row>
+    <row r="22" spans="1:10" ht="25.2" customHeight="1">
+      <c r="A22" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="71" t="s">
         <v>273</v>
       </c>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-    </row>
-    <row r="21" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A21" s="70" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="78">
-        <v>1994</v>
-      </c>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-    </row>
-    <row r="22" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A22" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="73" t="s">
-        <v>274</v>
-      </c>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
     </row>
     <row r="23" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A23" s="70" t="s">
+      <c r="A23" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A10:J10"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F21:J21"/>
     <mergeCell ref="F22:J22"/>
@@ -2279,21 +2294,6 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="F18:J18"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
@@ -2313,11 +2313,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.6">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
       <c r="D1" s="46"/>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2341,32 +2341,32 @@
       <c r="V1" s="46"/>
     </row>
     <row r="2" spans="1:22" ht="19.2" customHeight="1">
-      <c r="A2" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="81" t="s">
-        <v>281</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
+      <c r="A2" s="94" t="s">
+        <v>266</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="96" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
     </row>
     <row r="3" spans="1:22" ht="19.2" customHeight="1">
       <c r="A3" s="46"/>
@@ -2377,14 +2377,14 @@
       <c r="F3" s="46"/>
       <c r="G3" s="46"/>
       <c r="H3" s="46"/>
-      <c r="I3" s="80" t="s">
+      <c r="I3" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
       <c r="O3" s="46"/>
       <c r="P3" s="46"/>
       <c r="Q3" s="46"/>
@@ -2395,11 +2395,11 @@
       <c r="V3" s="46"/>
     </row>
     <row r="4" spans="1:22" ht="18.600000000000001" customHeight="1">
-      <c r="A4" s="79" t="s">
-        <v>282</v>
-      </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
+      <c r="A4" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="46"/>
       <c r="E4" s="46"/>
       <c r="F4" s="46"/>
@@ -2445,37 +2445,37 @@
       <c r="V5" s="46"/>
     </row>
     <row r="6" spans="1:22" ht="14.4" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="86" t="s">
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
-      <c r="P6" s="86"/>
-      <c r="Q6" s="86"/>
-      <c r="R6" s="86"/>
-      <c r="S6" s="86"/>
-      <c r="T6" s="86"/>
-      <c r="U6" s="86"/>
-      <c r="V6" s="86"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
+      <c r="R6" s="83"/>
+      <c r="S6" s="83"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="83"/>
+      <c r="V6" s="83"/>
     </row>
     <row r="7" spans="1:22" ht="147" customHeight="1">
-      <c r="A7" s="85"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
       <c r="D7" s="49" t="s">
         <v>20</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>25</v>
@@ -2510,10 +2510,10 @@
         <v>32</v>
       </c>
       <c r="O7" s="49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q7" s="49" t="s">
         <v>33</v>
@@ -2535,11 +2535,11 @@
       </c>
     </row>
     <row r="8" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A8" s="87" t="s">
-        <v>275</v>
-      </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="89"/>
+      <c r="A8" s="84" t="s">
+        <v>274</v>
+      </c>
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="51">
         <v>59</v>
       </c>
@@ -2577,11 +2577,11 @@
       </c>
     </row>
     <row r="9" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A9" s="93" t="s">
-        <v>276</v>
-      </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
+      <c r="A9" s="90" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="85"/>
+      <c r="C9" s="86"/>
       <c r="D9" s="51">
         <v>108</v>
       </c>
@@ -2615,11 +2615,11 @@
       </c>
     </row>
     <row r="10" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A10" s="93" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
+      <c r="A10" s="90" t="s">
+        <v>276</v>
+      </c>
+      <c r="B10" s="85"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="51">
         <v>108</v>
       </c>
@@ -2657,9 +2657,9 @@
       </c>
     </row>
     <row r="11" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="86"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
       <c r="F11" s="51"/>
@@ -2687,9 +2687,9 @@
       </c>
     </row>
     <row r="12" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="89"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
       <c r="F12" s="51"/>
@@ -2717,9 +2717,9 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="88"/>
-      <c r="C13" s="89"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="86"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
       <c r="F13" s="51"/>
@@ -2747,9 +2747,9 @@
       </c>
     </row>
     <row r="14" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
+      <c r="A14" s="91"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="93"/>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
       <c r="F14" s="51"/>
@@ -2777,9 +2777,9 @@
       </c>
     </row>
     <row r="15" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="96"/>
+      <c r="A15" s="91"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="93"/>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
@@ -2807,9 +2807,9 @@
       </c>
     </row>
     <row r="16" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="96"/>
+      <c r="A16" s="91"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
@@ -2837,9 +2837,9 @@
       </c>
     </row>
     <row r="17" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="96"/>
+      <c r="A17" s="91"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
@@ -2867,9 +2867,9 @@
       </c>
     </row>
     <row r="18" spans="1:22" s="53" customFormat="1" ht="28.95" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="92"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="89"/>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
@@ -2897,9 +2897,9 @@
       </c>
     </row>
     <row r="19" spans="1:22" s="53" customFormat="1" ht="28.2" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="92"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="89"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
@@ -2927,11 +2927,11 @@
       </c>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="84"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54">
         <f>SUM(E8:E19)</f>
@@ -3007,11 +3007,11 @@
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="82" t="s">
+      <c r="A21" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="84"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="81"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54">
         <f>E20</f>
@@ -3112,6 +3112,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="D2:V2"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A6:C7"/>
@@ -3128,11 +3133,6 @@
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="D2:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" orientation="landscape" r:id="rId1"/>
@@ -3150,30 +3150,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="19.2" customHeight="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
     </row>
     <row r="2" spans="1:22" ht="15.6">
       <c r="A2" s="10"/>
@@ -3200,37 +3200,37 @@
       <c r="V2" s="10"/>
     </row>
     <row r="3" spans="1:22" ht="14.4" customHeight="1">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111" t="s">
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
     </row>
     <row r="4" spans="1:22" ht="170.4" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
+      <c r="A4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
       <c r="D4" s="20" t="s">
         <v>20</v>
       </c>
@@ -3265,10 +3265,10 @@
         <v>32</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>33</v>
@@ -3290,11 +3290,11 @@
       </c>
     </row>
     <row r="5" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A5" s="100" t="s">
-        <v>278</v>
-      </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="102"/>
+      <c r="A5" s="98" t="s">
+        <v>277</v>
+      </c>
+      <c r="B5" s="99"/>
+      <c r="C5" s="100"/>
       <c r="D5" s="7">
         <v>25</v>
       </c>
@@ -3326,11 +3326,11 @@
       </c>
     </row>
     <row r="6" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A6" s="100" t="s">
-        <v>279</v>
-      </c>
-      <c r="B6" s="101"/>
-      <c r="C6" s="102"/>
+      <c r="A6" s="98" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="99"/>
+      <c r="C6" s="100"/>
       <c r="D6" s="7">
         <v>92</v>
       </c>
@@ -3362,11 +3362,11 @@
       </c>
     </row>
     <row r="7" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A7" s="100" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="102"/>
+      <c r="A7" s="98" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="99"/>
+      <c r="C7" s="100"/>
       <c r="D7" s="7">
         <v>59</v>
       </c>
@@ -3404,11 +3404,11 @@
       </c>
     </row>
     <row r="8" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A8" s="100" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="102"/>
+      <c r="A8" s="98" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="99"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="7">
         <v>108</v>
       </c>
@@ -3442,11 +3442,11 @@
       </c>
     </row>
     <row r="9" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A9" s="100" t="s">
-        <v>277</v>
-      </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="102"/>
+      <c r="A9" s="98" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="99"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="7">
         <v>108</v>
       </c>
@@ -3482,9 +3482,9 @@
       </c>
     </row>
     <row r="10" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="102"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -3512,9 +3512,9 @@
       </c>
     </row>
     <row r="11" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A11" s="100"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="102"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="100"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -3542,9 +3542,9 @@
       </c>
     </row>
     <row r="12" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="102"/>
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -3572,9 +3572,9 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A13" s="100"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="100"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -3602,9 +3602,9 @@
       </c>
     </row>
     <row r="14" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A14" s="103"/>
-      <c r="B14" s="104"/>
-      <c r="C14" s="105"/>
+      <c r="A14" s="109"/>
+      <c r="B14" s="110"/>
+      <c r="C14" s="111"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -3632,9 +3632,9 @@
       </c>
     </row>
     <row r="15" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A15" s="103"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="105"/>
+      <c r="A15" s="109"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="111"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -3662,9 +3662,9 @@
       </c>
     </row>
     <row r="16" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A16" s="107"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="109"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="103"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -3692,9 +3692,9 @@
       </c>
     </row>
     <row r="17" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A17" s="107"/>
-      <c r="B17" s="108"/>
-      <c r="C17" s="109"/>
+      <c r="A17" s="101"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="103"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -3722,11 +3722,11 @@
       </c>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="97" t="s">
+      <c r="A18" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="98"/>
-      <c r="C18" s="99"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="106"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
         <f>SUM(E5:E17)</f>
@@ -3802,11 +3802,11 @@
       </c>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="98"/>
-      <c r="C19" s="99"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="106"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
         <f>E18</f>
@@ -3882,11 +3882,11 @@
       </c>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="98"/>
-      <c r="C20" s="99"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="106"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
         <f>SUM(E18,'Осенний сем.'!E20)</f>
@@ -3962,11 +3962,11 @@
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="97" t="s">
+      <c r="A21" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="99"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="106"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
         <f>SUM(E19,'Осенний сем.'!E21)</f>
@@ -4067,6 +4067,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A16:C16"/>
@@ -4081,12 +4087,6 @@
     <mergeCell ref="A3:C4"/>
     <mergeCell ref="D3:V3"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" orientation="landscape" r:id="rId1"/>
@@ -4211,10 +4211,10 @@
         <v>54</v>
       </c>
       <c r="B8" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
@@ -4232,10 +4232,10 @@
         <v>55</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -4248,10 +4248,10 @@
         <v>56</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -4264,10 +4264,10 @@
         <v>57</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -4280,10 +4280,10 @@
         <v>58</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -4296,10 +4296,10 @@
         <v>59</v>
       </c>
       <c r="B13" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="38" t="s">
         <v>128</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>129</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -4312,10 +4312,10 @@
         <v>60</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -4328,10 +4328,10 @@
         <v>61</v>
       </c>
       <c r="B15" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="38" t="s">
         <v>131</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>132</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -4341,13 +4341,13 @@
     </row>
     <row r="16" spans="1:8" ht="13.95" customHeight="1">
       <c r="A16" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B16" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>92</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>93</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -4357,35 +4357,35 @@
     </row>
     <row r="17" spans="1:8" ht="52.8">
       <c r="A17" s="37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
-        <f t="shared" ref="E9:E23" si="0">D17</f>
+        <f t="shared" ref="E17:E23" si="0">D17</f>
         <v>0</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6">
-        <f t="shared" ref="G9:G23" si="1">F17</f>
+        <f t="shared" ref="G17:G23" si="1">F17</f>
         <v>0</v>
       </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" ht="26.4">
       <c r="A18" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B18" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>134</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>135</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6">
@@ -4401,13 +4401,13 @@
     </row>
     <row r="19" spans="1:8" ht="26.4">
       <c r="A19" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B19" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="38" t="s">
         <v>136</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>137</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6">
@@ -4423,13 +4423,13 @@
     </row>
     <row r="20" spans="1:8" ht="26.4">
       <c r="A20" s="37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>138</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>139</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6">
@@ -4445,13 +4445,13 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6">
@@ -4467,13 +4467,13 @@
     </row>
     <row r="22" spans="1:8" ht="55.2" customHeight="1">
       <c r="A22" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>141</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>142</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6">
@@ -4489,13 +4489,13 @@
     </row>
     <row r="23" spans="1:8" ht="26.4">
       <c r="A23" s="37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6">
@@ -4547,13 +4547,13 @@
     </row>
     <row r="26" spans="1:8" ht="79.8">
       <c r="A26" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B26" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="41" t="s">
         <v>155</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>156</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6">
@@ -4569,13 +4569,13 @@
     </row>
     <row r="27" spans="1:8" ht="26.4">
       <c r="A27" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B27" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="41" t="s">
         <v>153</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>154</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6">
@@ -4615,7 +4615,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="114" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="115"/>
       <c r="C29" s="115"/>
@@ -4627,13 +4627,13 @@
     </row>
     <row r="30" spans="1:8" ht="27">
       <c r="A30" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6">
@@ -4649,13 +4649,13 @@
     </row>
     <row r="31" spans="1:8" ht="27">
       <c r="A31" s="37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6">
@@ -4671,13 +4671,13 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -4690,13 +4690,13 @@
     </row>
     <row r="33" spans="1:8" ht="27">
       <c r="A33" s="37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6">
@@ -4712,13 +4712,13 @@
     </row>
     <row r="34" spans="1:8" ht="40.200000000000003">
       <c r="A34" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B34" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="42" t="s">
         <v>166</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>167</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6">
@@ -5121,13 +5121,13 @@
     </row>
     <row r="2" spans="1:8" ht="40.200000000000003">
       <c r="A2" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="43">
@@ -5143,13 +5143,13 @@
     </row>
     <row r="3" spans="1:8" ht="27">
       <c r="A3" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="43">
@@ -5165,13 +5165,13 @@
     </row>
     <row r="4" spans="1:8" ht="27">
       <c r="A4" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="43">
@@ -5211,7 +5211,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" s="125"/>
       <c r="C6" s="2"/>
@@ -5609,7 +5609,7 @@
     </row>
     <row r="7" spans="1:8" ht="20.399999999999999" customHeight="1">
       <c r="A7" s="126" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -5620,13 +5620,13 @@
     </row>
     <row r="8" spans="1:8" ht="22.2" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
@@ -5642,13 +5642,13 @@
     </row>
     <row r="9" spans="1:8" ht="27.6" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6">
@@ -5664,13 +5664,13 @@
     </row>
     <row r="10" spans="1:8" ht="28.95" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6">
@@ -5686,13 +5686,13 @@
     </row>
     <row r="11" spans="1:8" ht="43.2" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6">
@@ -5708,13 +5708,13 @@
     </row>
     <row r="12" spans="1:8" ht="28.95" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
@@ -5730,13 +5730,13 @@
     </row>
     <row r="13" spans="1:8" ht="43.2" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
@@ -5752,13 +5752,13 @@
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6">
@@ -5774,10 +5774,10 @@
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
@@ -5793,10 +5793,10 @@
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6">
@@ -5812,10 +5812,10 @@
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1">
       <c r="B17" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="18" spans="1:8" ht="29.4" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6">
@@ -5850,13 +5850,13 @@
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6">
@@ -5872,13 +5872,13 @@
     </row>
     <row r="20" spans="1:8" ht="28.95" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6">
@@ -5894,13 +5894,13 @@
     </row>
     <row r="21" spans="1:8" ht="27.6" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6">
@@ -5916,13 +5916,13 @@
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6">
@@ -5962,7 +5962,7 @@
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1">
       <c r="A24" s="127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="127"/>
       <c r="C24" s="127"/>
@@ -5974,13 +5974,13 @@
     </row>
     <row r="25" spans="1:8" ht="41.4" customHeight="1">
       <c r="A25" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6">
@@ -5996,13 +5996,13 @@
     </row>
     <row r="26" spans="1:8" ht="27" customHeight="1">
       <c r="A26" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6">
@@ -6018,13 +6018,13 @@
     </row>
     <row r="27" spans="1:8" ht="42" customHeight="1">
       <c r="A27" s="25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6">
@@ -6040,13 +6040,13 @@
     </row>
     <row r="28" spans="1:8" ht="40.200000000000003" customHeight="1">
       <c r="A28" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6">
@@ -6062,13 +6062,13 @@
     </row>
     <row r="29" spans="1:8" ht="39.6" customHeight="1">
       <c r="A29" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6">
@@ -6108,7 +6108,7 @@
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1">
       <c r="A31" s="125" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B31" s="125"/>
       <c r="C31" s="2"/>
@@ -6186,7 +6186,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
       <c r="A1" s="128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" s="128"/>
       <c r="C1" s="128"/>
@@ -6197,15 +6197,15 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="19.2" customHeight="1">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="134" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8">
@@ -6284,7 +6284,7 @@
     </row>
     <row r="7" spans="1:8" ht="42.6" customHeight="1">
       <c r="A7" s="126" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
       <c r="A8" s="37" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="6"/>
@@ -6317,10 +6317,10 @@
     <row r="9" spans="1:8" ht="27" customHeight="1">
       <c r="A9" s="37"/>
       <c r="B9" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6">
@@ -6337,10 +6337,10 @@
     <row r="10" spans="1:8" ht="18" customHeight="1">
       <c r="A10" s="37"/>
       <c r="B10" s="44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6">
@@ -6357,10 +6357,10 @@
     <row r="11" spans="1:8" ht="18" customHeight="1">
       <c r="A11" s="37"/>
       <c r="B11" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6">
@@ -6377,10 +6377,10 @@
     <row r="12" spans="1:8" ht="18" customHeight="1">
       <c r="A12" s="37"/>
       <c r="B12" s="44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
@@ -6397,10 +6397,10 @@
     <row r="13" spans="1:8" ht="18" customHeight="1">
       <c r="A13" s="37"/>
       <c r="B13" s="44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
@@ -6417,10 +6417,10 @@
     <row r="14" spans="1:8" ht="27.6" customHeight="1">
       <c r="A14" s="37"/>
       <c r="B14" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6">
@@ -6437,10 +6437,10 @@
     <row r="15" spans="1:8" ht="27.6" customHeight="1">
       <c r="A15" s="37"/>
       <c r="B15" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
@@ -6457,10 +6457,10 @@
     <row r="16" spans="1:8" ht="40.950000000000003" customHeight="1">
       <c r="A16" s="37"/>
       <c r="B16" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6">
@@ -6476,13 +6476,13 @@
     </row>
     <row r="17" spans="1:8" ht="42" customHeight="1">
       <c r="A17" s="37" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B17" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="38" t="s">
         <v>237</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>238</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="18" spans="1:8" ht="52.2" customHeight="1">
       <c r="A18" s="37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="6"/>
@@ -6519,10 +6519,10 @@
     <row r="19" spans="1:8" ht="18" customHeight="1">
       <c r="A19" s="37"/>
       <c r="B19" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6">
@@ -6539,10 +6539,10 @@
     <row r="20" spans="1:8" ht="18" customHeight="1">
       <c r="A20" s="37"/>
       <c r="B20" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6">
@@ -6559,10 +6559,10 @@
     <row r="21" spans="1:8" ht="18" customHeight="1">
       <c r="A21" s="37"/>
       <c r="B21" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6">
@@ -6578,10 +6578,10 @@
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1">
       <c r="A22" s="37" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C22" s="38"/>
       <c r="D22" s="6"/>
@@ -6599,10 +6599,10 @@
     <row r="23" spans="1:8" ht="18" customHeight="1">
       <c r="A23" s="37"/>
       <c r="B23" s="44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6">
@@ -6619,10 +6619,10 @@
     <row r="24" spans="1:8" ht="18" customHeight="1">
       <c r="A24" s="37"/>
       <c r="B24" s="44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6">
@@ -6639,10 +6639,10 @@
     <row r="25" spans="1:8" ht="18" customHeight="1">
       <c r="A25" s="37"/>
       <c r="B25" s="44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6">
@@ -6659,10 +6659,10 @@
     <row r="26" spans="1:8" ht="18" customHeight="1">
       <c r="A26" s="37"/>
       <c r="B26" s="44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6">
@@ -6679,10 +6679,10 @@
     <row r="27" spans="1:8" ht="27" customHeight="1">
       <c r="A27" s="37"/>
       <c r="B27" s="44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6">
@@ -6698,13 +6698,13 @@
     </row>
     <row r="28" spans="1:8" ht="40.200000000000003" customHeight="1">
       <c r="A28" s="37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6">
@@ -6720,13 +6720,13 @@
     </row>
     <row r="29" spans="1:8" ht="40.950000000000003" customHeight="1">
       <c r="A29" s="37" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6">
@@ -6766,7 +6766,7 @@
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1">
       <c r="A31" s="127" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B31" s="127"/>
       <c r="C31" s="127"/>
@@ -6849,10 +6849,10 @@
       <c r="H35" s="1"/>
     </row>
     <row r="36" spans="1:8" ht="25.95" customHeight="1">
-      <c r="A36" s="138" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="138"/>
+      <c r="A36" s="135" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="135"/>
       <c r="C36" s="2"/>
       <c r="D36" s="5">
         <f>SUM(D35,D30)</f>
@@ -6873,36 +6873,36 @@
       <c r="H36" s="1"/>
     </row>
     <row r="37" spans="1:8" ht="28.95" customHeight="1">
-      <c r="A37" s="136" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="136"/>
-      <c r="C37" s="136"/>
-      <c r="D37" s="136"/>
-      <c r="E37" s="136"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="136"/>
+      <c r="A37" s="133" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="133"/>
+      <c r="C37" s="133"/>
+      <c r="D37" s="133"/>
+      <c r="E37" s="133"/>
+      <c r="F37" s="133"/>
+      <c r="G37" s="133"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38" spans="1:8" ht="66" customHeight="1">
       <c r="A38" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="C38" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C38" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="18" t="s">
+      <c r="E38" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="133" t="s">
+      <c r="F38" s="136"/>
+      <c r="G38" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="F38" s="133"/>
-      <c r="G38" s="17" t="s">
-        <v>106</v>
       </c>
       <c r="H38" s="1"/>
     </row>
@@ -6911,8 +6911,8 @@
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="134"/>
-      <c r="F39" s="135"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="138"/>
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
     </row>
@@ -6921,8 +6921,8 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="134"/>
-      <c r="F40" s="135"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="138"/>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
     </row>
@@ -6931,8 +6931,8 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="134"/>
-      <c r="F41" s="135"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="138"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
     </row>
@@ -6941,8 +6941,8 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="135"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="138"/>
       <c r="G42" s="2"/>
       <c r="H42" s="1"/>
     </row>
@@ -6978,6 +6978,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -6991,11 +6996,6 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -7014,520 +7014,617 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.95" customHeight="1">
-      <c r="A1" s="139" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
+      <c r="A1" s="153" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
     </row>
     <row r="2" spans="1:9" ht="52.2" customHeight="1">
       <c r="A2" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="145" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="C2" s="145"/>
+      <c r="D2" s="148" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="148"/>
+      <c r="F2" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="149" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="149"/>
-      <c r="F2" s="33" t="s">
+      <c r="G2" s="149" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="150" t="s">
+      <c r="H2" s="149"/>
+      <c r="I2" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="H2" s="150"/>
-      <c r="I2" s="17" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.95" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="19.95" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="19.95" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="19.95" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="140"/>
-      <c r="E6" s="142"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="144"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="135"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="138"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" ht="19.95" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="142"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="144"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="135"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="138"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" ht="19.95" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="142"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="144"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="135"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="138"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" ht="19.95" customHeight="1">
       <c r="A9" s="2"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="142"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="144"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="135"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="138"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" ht="19.95" customHeight="1">
       <c r="A10" s="2"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="142"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="138"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="144"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="135"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="138"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="19.95" customHeight="1">
       <c r="A11" s="2"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="135"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="142"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="144"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="134"/>
-      <c r="H11" s="135"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="138"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="142"/>
+      <c r="B12" s="137"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="144"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="135"/>
+      <c r="G12" s="137"/>
+      <c r="H12" s="138"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="140"/>
-      <c r="E13" s="142"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="144"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="134"/>
-      <c r="H13" s="135"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="138"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="140"/>
-      <c r="E14" s="142"/>
+      <c r="B14" s="137"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="144"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="135"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="138"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1">
       <c r="A15" s="2"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="142"/>
+      <c r="B15" s="137"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="144"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="135"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="138"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="19.95" customHeight="1">
       <c r="A16" s="2"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="143"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="19.95" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="111"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="139"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="19.95" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="143"/>
+      <c r="B18" s="108"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="111"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="36" customHeight="1">
-      <c r="A19" s="151" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="151"/>
-      <c r="C19" s="151"/>
-      <c r="D19" s="151"/>
-      <c r="E19" s="151"/>
-      <c r="F19" s="151"/>
-      <c r="G19" s="151"/>
-      <c r="H19" s="151"/>
-      <c r="I19" s="151"/>
+      <c r="A19" s="150" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="150"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="150"/>
     </row>
     <row r="20" spans="1:9" ht="54" customHeight="1">
       <c r="A20" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="153" t="s">
+      <c r="C20" s="142"/>
+      <c r="D20" s="146" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="147"/>
+      <c r="F20" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="154"/>
-      <c r="D20" s="147" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" s="148"/>
-      <c r="F20" s="18" t="s">
+      <c r="G20" s="136" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="133" t="s">
+      <c r="H20" s="136"/>
+      <c r="I20" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="17" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="19.95" customHeight="1">
       <c r="A21" s="2"/>
-      <c r="B21" s="134"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="135"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="138"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="135"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="138"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" ht="19.95" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="135"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="138"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="135"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="138"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" ht="19.95" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="135"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="138"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="135"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="138"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" ht="19.95" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="138"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="135"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="138"/>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9" ht="19.95" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="134"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="134"/>
-      <c r="E25" s="135"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="138"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="135"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="138"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" ht="19.95" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="135"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="138"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="135"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="138"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" ht="19.95" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="135"/>
+      <c r="B27" s="137"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="138"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="135"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="138"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" ht="19.95" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="134"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="138"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="135"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="138"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="19.95" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="135"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="138"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="135"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="138"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" ht="19.95" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="134"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="135"/>
+      <c r="B30" s="137"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="138"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="135"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="138"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" ht="19.95" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="135"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="135"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="138"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="135"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="138"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" ht="19.95" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="134"/>
-      <c r="C32" s="135"/>
-      <c r="D32" s="134"/>
-      <c r="E32" s="135"/>
+      <c r="B32" s="137"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="138"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="134"/>
-      <c r="H32" s="135"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="138"/>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" ht="19.95" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="135"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="135"/>
+      <c r="B33" s="137"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="138"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="135"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="138"/>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="134"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="135"/>
+      <c r="B34" s="137"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="138"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="134"/>
-      <c r="H34" s="135"/>
+      <c r="G34" s="137"/>
+      <c r="H34" s="138"/>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" ht="19.95" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="134"/>
-      <c r="C35" s="135"/>
-      <c r="D35" s="134"/>
-      <c r="E35" s="135"/>
+      <c r="B35" s="137"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="138"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="134"/>
-      <c r="H35" s="135"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="138"/>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1">
-      <c r="A36" s="136" t="s">
+      <c r="A36" s="133" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="133"/>
+      <c r="C36" s="133"/>
+      <c r="D36" s="133"/>
+      <c r="E36" s="133"/>
+      <c r="F36" s="133"/>
+      <c r="G36" s="133"/>
+      <c r="H36" s="133"/>
+      <c r="I36" s="133"/>
+    </row>
+    <row r="37" spans="1:9" ht="21" customHeight="1">
+      <c r="A37" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="B36" s="136"/>
-      <c r="C36" s="136"/>
-      <c r="D36" s="136"/>
-      <c r="E36" s="136"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="136"/>
-      <c r="H36" s="136"/>
-      <c r="I36" s="136"/>
-    </row>
-    <row r="37" spans="1:9" ht="21" customHeight="1">
-      <c r="A37" s="152" t="s">
+      <c r="B37" s="140"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+    </row>
+    <row r="38" spans="1:9" ht="35.4" customHeight="1">
+      <c r="A38" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="152"/>
-      <c r="C37" s="152"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="152"/>
-      <c r="F37" s="152"/>
-      <c r="G37" s="152"/>
-      <c r="H37" s="152"/>
-      <c r="I37" s="152"/>
-    </row>
-    <row r="38" spans="1:9" ht="35.4" customHeight="1">
-      <c r="A38" s="145" t="s">
+      <c r="B38" s="152"/>
+      <c r="C38" s="152"/>
+      <c r="D38" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="145"/>
-      <c r="C38" s="145"/>
-      <c r="D38" s="31" t="s">
+      <c r="E38" s="151" t="s">
         <v>112</v>
       </c>
-      <c r="E38" s="144" t="s">
+      <c r="F38" s="151"/>
+      <c r="G38" s="107" t="s">
         <v>113</v>
       </c>
-      <c r="F38" s="144"/>
-      <c r="G38" s="110" t="s">
-        <v>114</v>
-      </c>
-      <c r="H38" s="110"/>
-      <c r="I38" s="110"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="107"/>
     </row>
     <row r="39" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A39" s="143"/>
-      <c r="B39" s="143"/>
-      <c r="C39" s="143"/>
+      <c r="A39" s="139"/>
+      <c r="B39" s="139"/>
+      <c r="C39" s="139"/>
       <c r="D39" s="3"/>
-      <c r="E39" s="143"/>
-      <c r="F39" s="143"/>
-      <c r="G39" s="143"/>
-      <c r="H39" s="143"/>
-      <c r="I39" s="143"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="139"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="139"/>
     </row>
     <row r="40" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A40" s="140"/>
-      <c r="B40" s="141"/>
-      <c r="C40" s="142"/>
+      <c r="A40" s="143"/>
+      <c r="B40" s="154"/>
+      <c r="C40" s="144"/>
       <c r="D40" s="3"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="141"/>
-      <c r="I40" s="142"/>
+      <c r="E40" s="143"/>
+      <c r="F40" s="144"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="154"/>
+      <c r="I40" s="144"/>
     </row>
     <row r="41" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A41" s="143"/>
-      <c r="B41" s="143"/>
-      <c r="C41" s="143"/>
+      <c r="A41" s="139"/>
+      <c r="B41" s="139"/>
+      <c r="C41" s="139"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="143"/>
-      <c r="F41" s="143"/>
-      <c r="G41" s="143"/>
-      <c r="H41" s="143"/>
-      <c r="I41" s="143"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="139"/>
+      <c r="H41" s="139"/>
+      <c r="I41" s="139"/>
     </row>
     <row r="42" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="143"/>
-      <c r="C42" s="143"/>
+      <c r="A42" s="139"/>
+      <c r="B42" s="139"/>
+      <c r="C42" s="139"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="143"/>
-      <c r="I42" s="143"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="139"/>
     </row>
     <row r="43" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A43" s="143"/>
-      <c r="B43" s="143"/>
-      <c r="C43" s="143"/>
+      <c r="A43" s="139"/>
+      <c r="B43" s="139"/>
+      <c r="C43" s="139"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="143"/>
-      <c r="F43" s="143"/>
-      <c r="G43" s="143"/>
-      <c r="H43" s="143"/>
-      <c r="I43" s="143"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
+      <c r="G43" s="139"/>
+      <c r="H43" s="139"/>
+      <c r="I43" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="121">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="A36:I36"/>
@@ -7552,103 +7649,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G22:H22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
@@ -7672,71 +7672,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="155" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
+      <c r="A1" s="168" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
+      <c r="G1" s="168"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
     </row>
     <row r="2" spans="1:10" ht="20.399999999999999" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
-      <c r="A3" s="170" t="s">
-        <v>283</v>
-      </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="170"/>
-      <c r="I3" s="170"/>
+      <c r="A3" s="155" t="s">
+        <v>282</v>
+      </c>
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
     </row>
     <row r="4" spans="1:10" ht="15.6">
-      <c r="A4" s="172" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="172"/>
-      <c r="C4" s="172"/>
-      <c r="D4" s="172"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="172"/>
-      <c r="G4" s="172"/>
+      <c r="A4" s="157" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="157"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="157"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="157"/>
+      <c r="G4" s="157"/>
       <c r="H4" s="57">
         <v>0.43</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="171"/>
-      <c r="B5" s="171"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
+      <c r="A5" s="156"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="156"/>
+      <c r="H5" s="156"/>
+      <c r="I5" s="156"/>
     </row>
     <row r="6" spans="1:10" ht="29.4" customHeight="1">
       <c r="A6" s="162" t="s">
@@ -7758,56 +7758,56 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.6">
-      <c r="A7" s="167" t="s">
+      <c r="A7" s="163" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="167"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="167"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="163"/>
+      <c r="D7" s="163"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="163"/>
       <c r="G7" s="61"/>
       <c r="H7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="15.6">
-      <c r="A8" s="167" t="s">
+      <c r="A8" s="163" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="167"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="163"/>
+      <c r="D8" s="163"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="163"/>
       <c r="G8" s="61"/>
       <c r="H8" s="61"/>
       <c r="I8" s="60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A9" s="168" t="s">
+      <c r="A9" s="164" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="168"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="168"/>
+      <c r="B9" s="164"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="164"/>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
       <c r="G9" s="61"/>
       <c r="H9" s="61"/>
       <c r="I9" s="62" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6">
-      <c r="A10" s="167" t="s">
+      <c r="A10" s="163" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="167"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
       <c r="G10" s="61"/>
       <c r="H10" s="61"/>
       <c r="I10" s="63">
@@ -7817,133 +7817,133 @@
       <c r="J10" s="69"/>
     </row>
     <row r="11" spans="1:10" ht="23.4" customHeight="1">
-      <c r="A11" s="169" t="s">
+      <c r="A11" s="165" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="169"/>
-      <c r="C11" s="169"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="169"/>
-      <c r="F11" s="169"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
       <c r="I11" s="63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="41.4" customHeight="1">
+      <c r="A12" s="158"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="158"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="158"/>
+      <c r="G12" s="158"/>
+      <c r="H12" s="158"/>
+      <c r="I12" s="158"/>
+    </row>
+    <row r="13" spans="1:10" ht="31.95" customHeight="1">
+      <c r="A13" s="159" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="41.4" customHeight="1">
-      <c r="A12" s="173"/>
-      <c r="B12" s="173"/>
-      <c r="C12" s="173"/>
-      <c r="D12" s="173"/>
-      <c r="E12" s="173"/>
-      <c r="F12" s="173"/>
-      <c r="G12" s="173"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="173"/>
-    </row>
-    <row r="13" spans="1:10" ht="31.95" customHeight="1">
-      <c r="A13" s="165" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="166"/>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
+      <c r="B13" s="160"/>
+      <c r="C13" s="160"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="160"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="160"/>
     </row>
     <row r="14" spans="1:10" ht="29.4" customHeight="1">
-      <c r="A14" s="164" t="s">
+      <c r="A14" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="161"/>
+      <c r="C14" s="161"/>
+      <c r="D14" s="161"/>
+      <c r="E14" s="161"/>
+      <c r="F14" s="161"/>
+      <c r="G14" s="167" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="164"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="164"/>
-      <c r="E14" s="164"/>
-      <c r="F14" s="164"/>
-      <c r="G14" s="163" t="s">
+      <c r="H14" s="161"/>
+      <c r="I14" s="161"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A15" s="166"/>
+      <c r="B15" s="166"/>
+      <c r="C15" s="166"/>
+      <c r="D15" s="166"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="166"/>
+      <c r="G15" s="166"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="166"/>
+    </row>
+    <row r="16" spans="1:10" ht="19.95" customHeight="1">
+      <c r="A16" s="166"/>
+      <c r="B16" s="166"/>
+      <c r="C16" s="166"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="166"/>
+      <c r="F16" s="166"/>
+      <c r="G16" s="166"/>
+      <c r="H16" s="166"/>
+      <c r="I16" s="166"/>
+    </row>
+    <row r="17" spans="1:9" ht="19.95" customHeight="1">
+      <c r="A17" s="166"/>
+      <c r="B17" s="166"/>
+      <c r="C17" s="166"/>
+      <c r="D17" s="166"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="166"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="166"/>
+    </row>
+    <row r="18" spans="1:9" ht="19.95" customHeight="1">
+      <c r="A18" s="166"/>
+      <c r="B18" s="166"/>
+      <c r="C18" s="166"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="166"/>
+      <c r="G18" s="166"/>
+      <c r="H18" s="166"/>
+      <c r="I18" s="166"/>
+    </row>
+    <row r="19" spans="1:9" ht="19.95" customHeight="1">
+      <c r="A19" s="166"/>
+      <c r="B19" s="166"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="166"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="166"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="166"/>
+      <c r="I19" s="166"/>
+    </row>
+    <row r="20" spans="1:9" ht="33.6" customHeight="1">
+      <c r="A20" s="172" t="s">
         <v>75</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="164"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A15" s="158"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="158"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="158"/>
-      <c r="I15" s="158"/>
-    </row>
-    <row r="16" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A16" s="158"/>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="158"/>
-    </row>
-    <row r="17" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A17" s="158"/>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
-      <c r="F17" s="158"/>
-      <c r="G17" s="158"/>
-      <c r="H17" s="158"/>
-      <c r="I17" s="158"/>
-    </row>
-    <row r="18" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A18" s="158"/>
-      <c r="B18" s="158"/>
-      <c r="C18" s="158"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="158"/>
-      <c r="I18" s="158"/>
-    </row>
-    <row r="19" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A19" s="158"/>
-      <c r="B19" s="158"/>
-      <c r="C19" s="158"/>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
-      <c r="F19" s="158"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="158"/>
-      <c r="I19" s="158"/>
-    </row>
-    <row r="20" spans="1:9" ht="33.6" customHeight="1">
-      <c r="A20" s="160" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="161"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="161"/>
-      <c r="E20" s="161"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="161"/>
-      <c r="H20" s="161"/>
-      <c r="I20" s="161"/>
+      <c r="B20" s="173"/>
+      <c r="C20" s="173"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="173"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="173"/>
     </row>
     <row r="21" spans="1:9" ht="21" customHeight="1">
       <c r="A21" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="162" t="s">
         <v>77</v>
-      </c>
-      <c r="B21" s="162" t="s">
-        <v>78</v>
       </c>
       <c r="C21" s="162"/>
       <c r="D21" s="162"/>
@@ -7955,164 +7955,139 @@
     </row>
     <row r="22" spans="1:9" ht="16.95" customHeight="1">
       <c r="A22" s="66"/>
-      <c r="B22" s="158"/>
-      <c r="C22" s="158"/>
-      <c r="D22" s="158"/>
-      <c r="E22" s="158"/>
-      <c r="F22" s="158"/>
-      <c r="G22" s="158"/>
-      <c r="H22" s="158"/>
-      <c r="I22" s="158"/>
+      <c r="B22" s="166"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="166"/>
     </row>
     <row r="23" spans="1:9" ht="16.95" customHeight="1">
       <c r="A23" s="66"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="158"/>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="158"/>
-      <c r="I23" s="158"/>
+      <c r="B23" s="166"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="166"/>
+      <c r="H23" s="166"/>
+      <c r="I23" s="166"/>
     </row>
     <row r="24" spans="1:9" ht="16.95" customHeight="1">
       <c r="A24" s="66"/>
-      <c r="B24" s="158"/>
-      <c r="C24" s="158"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
+      <c r="B24" s="166"/>
+      <c r="C24" s="166"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="166"/>
+      <c r="F24" s="166"/>
+      <c r="G24" s="166"/>
+      <c r="H24" s="166"/>
+      <c r="I24" s="166"/>
     </row>
     <row r="25" spans="1:9" ht="16.95" customHeight="1">
       <c r="A25" s="66"/>
-      <c r="B25" s="158"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
+      <c r="B25" s="166"/>
+      <c r="C25" s="166"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="166"/>
+      <c r="I25" s="166"/>
     </row>
     <row r="26" spans="1:9" ht="16.95" customHeight="1">
       <c r="A26" s="66"/>
-      <c r="B26" s="158"/>
-      <c r="C26" s="158"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="158"/>
-      <c r="G26" s="158"/>
-      <c r="H26" s="158"/>
-      <c r="I26" s="158"/>
+      <c r="B26" s="166"/>
+      <c r="C26" s="166"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="166"/>
+      <c r="F26" s="166"/>
+      <c r="G26" s="166"/>
+      <c r="H26" s="166"/>
+      <c r="I26" s="166"/>
     </row>
     <row r="27" spans="1:9" ht="16.95" customHeight="1">
       <c r="A27" s="66"/>
-      <c r="B27" s="158"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="158"/>
-      <c r="G27" s="158"/>
-      <c r="H27" s="158"/>
-      <c r="I27" s="158"/>
+      <c r="B27" s="166"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="166"/>
+      <c r="G27" s="166"/>
+      <c r="H27" s="166"/>
+      <c r="I27" s="166"/>
     </row>
     <row r="28" spans="1:9" ht="16.95" customHeight="1">
       <c r="A28" s="66"/>
-      <c r="B28" s="158"/>
-      <c r="C28" s="158"/>
-      <c r="D28" s="158"/>
-      <c r="E28" s="158"/>
-      <c r="F28" s="158"/>
-      <c r="G28" s="158"/>
-      <c r="H28" s="158"/>
-      <c r="I28" s="158"/>
+      <c r="B28" s="166"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="166"/>
+      <c r="H28" s="166"/>
+      <c r="I28" s="166"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="159"/>
-      <c r="B29" s="159"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="159"/>
-      <c r="H29" s="159"/>
-      <c r="I29" s="159"/>
+      <c r="A29" s="171"/>
+      <c r="B29" s="171"/>
+      <c r="C29" s="171"/>
+      <c r="D29" s="171"/>
+      <c r="E29" s="171"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="171"/>
+      <c r="H29" s="171"/>
+      <c r="I29" s="171"/>
     </row>
     <row r="30" spans="1:9" ht="60" customHeight="1">
-      <c r="A30" s="156" t="s">
+      <c r="A30" s="169" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="169"/>
+      <c r="C30" s="169"/>
+      <c r="D30" s="169"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="169" t="s">
+        <v>279</v>
+      </c>
+      <c r="G30" s="169"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="67"/>
+    </row>
+    <row r="31" spans="1:9" ht="19.95" customHeight="1">
+      <c r="A31" s="170" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="156"/>
-      <c r="C30" s="156"/>
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156" t="s">
-        <v>280</v>
-      </c>
-      <c r="G30" s="156"/>
-      <c r="H30" s="156"/>
-      <c r="I30" s="67"/>
-    </row>
-    <row r="31" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A31" s="157" t="s">
+      <c r="B31" s="170"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="170"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="170" t="s">
+        <v>267</v>
+      </c>
+      <c r="G31" s="170"/>
+      <c r="H31" s="170"/>
+      <c r="I31" s="68"/>
+    </row>
+    <row r="32" spans="1:9" ht="19.95" customHeight="1">
+      <c r="A32" s="169" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="157"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="157" t="s">
-        <v>268</v>
-      </c>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="68"/>
-    </row>
-    <row r="32" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A32" s="156" t="s">
+      <c r="B32" s="169"/>
+      <c r="C32" s="169"/>
+      <c r="D32" s="169"/>
+      <c r="E32" s="169"/>
+      <c r="F32" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="156"/>
-      <c r="C32" s="156"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="157" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="157"/>
-      <c r="H32" s="157"/>
+      <c r="G32" s="170"/>
+      <c r="H32" s="170"/>
       <c r="I32" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G16:I16"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A31:E31"/>
@@ -8129,6 +8104,31 @@
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A12:I12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>

--- a/Templates/IndividualPlanTemplate.xlsx
+++ b/Templates/IndividualPlanTemplate.xlsx
@@ -1388,32 +1388,41 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1460,28 +1469,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1490,30 +1508,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1577,6 +1577,15 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1586,18 +1595,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1607,41 +1643,50 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1654,51 +1699,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2006,7 +2006,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2021,60 +2021,60 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
+      <c r="A1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1"/>
     <row r="6" spans="1:10" ht="30" customHeight="1"/>
@@ -2082,208 +2082,193 @@
     <row r="8" spans="1:10" ht="30" customHeight="1"/>
     <row r="9" spans="1:10" ht="30" customHeight="1"/>
     <row r="10" spans="1:10" ht="39.6" customHeight="1">
-      <c r="A10" s="75" t="s">
+      <c r="A10" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="75"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
     </row>
     <row r="11" spans="1:10" ht="40.200000000000003" customHeight="1">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
     </row>
     <row r="12" spans="1:10" ht="40.200000000000003" customHeight="1">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="76"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="75"/>
     </row>
     <row r="13" spans="1:10" ht="28.95" customHeight="1"/>
     <row r="14" spans="1:10" ht="34.200000000000003" customHeight="1"/>
     <row r="15" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="77" t="s">
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
     </row>
     <row r="16" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A16" s="72" t="s">
+      <c r="A16" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="78" t="s">
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="72" t="s">
         <v>268</v>
       </c>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
     </row>
     <row r="17" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="71" t="s">
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="73" t="s">
         <v>269</v>
       </c>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
     </row>
     <row r="18" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="71" t="s">
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="73" t="s">
         <v>270</v>
       </c>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="73"/>
     </row>
     <row r="19" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="70" t="s">
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="78" t="s">
         <v>271</v>
       </c>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="70"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
     </row>
     <row r="20" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="71" t="s">
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="73" t="s">
         <v>272</v>
       </c>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="73"/>
     </row>
     <row r="21" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A21" s="72" t="s">
+      <c r="A21" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="70">
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="78">
         <v>1994</v>
       </c>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
     </row>
     <row r="22" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="71" t="s">
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="73" t="s">
         <v>273</v>
       </c>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
     </row>
     <row r="23" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="70"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A10:J10"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F21:J21"/>
     <mergeCell ref="F22:J22"/>
@@ -2294,6 +2279,21 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F18:J18"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
@@ -2313,11 +2313,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.6">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
       <c r="D1" s="46"/>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2341,32 +2341,32 @@
       <c r="V1" s="46"/>
     </row>
     <row r="2" spans="1:22" ht="19.2" customHeight="1">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="79" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="96" t="s">
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
-      <c r="S2" s="96"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="96"/>
-      <c r="V2" s="96"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
     </row>
     <row r="3" spans="1:22" ht="19.2" customHeight="1">
       <c r="A3" s="46"/>
@@ -2377,14 +2377,14 @@
       <c r="F3" s="46"/>
       <c r="G3" s="46"/>
       <c r="H3" s="46"/>
-      <c r="I3" s="95" t="s">
+      <c r="I3" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="95"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
       <c r="O3" s="46"/>
       <c r="P3" s="46"/>
       <c r="Q3" s="46"/>
@@ -2395,11 +2395,11 @@
       <c r="V3" s="46"/>
     </row>
     <row r="4" spans="1:22" ht="18.600000000000001" customHeight="1">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="79" t="s">
         <v>281</v>
       </c>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
       <c r="D4" s="46"/>
       <c r="E4" s="46"/>
       <c r="F4" s="46"/>
@@ -2445,37 +2445,37 @@
       <c r="V5" s="46"/>
     </row>
     <row r="6" spans="1:22" ht="14.4" customHeight="1">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="83" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="83"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
+      <c r="L6" s="86"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="86"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="86"/>
+      <c r="T6" s="86"/>
+      <c r="U6" s="86"/>
+      <c r="V6" s="86"/>
     </row>
     <row r="7" spans="1:22" ht="147" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
       <c r="D7" s="49" t="s">
         <v>20</v>
       </c>
@@ -2535,11 +2535,11 @@
       </c>
     </row>
     <row r="8" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="87" t="s">
         <v>274</v>
       </c>
-      <c r="B8" s="85"/>
-      <c r="C8" s="86"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="51">
         <v>59</v>
       </c>
@@ -2577,11 +2577,11 @@
       </c>
     </row>
     <row r="9" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="93" t="s">
         <v>275</v>
       </c>
-      <c r="B9" s="85"/>
-      <c r="C9" s="86"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
       <c r="D9" s="51">
         <v>108</v>
       </c>
@@ -2615,11 +2615,11 @@
       </c>
     </row>
     <row r="10" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="93" t="s">
         <v>276</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="86"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="51">
         <v>108</v>
       </c>
@@ -2657,9 +2657,9 @@
       </c>
     </row>
     <row r="11" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="86"/>
+      <c r="A11" s="93"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
       <c r="F11" s="51"/>
@@ -2687,9 +2687,9 @@
       </c>
     </row>
     <row r="12" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="86"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="89"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
       <c r="F12" s="51"/>
@@ -2717,9 +2717,9 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A13" s="90"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="86"/>
+      <c r="A13" s="93"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="89"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
       <c r="F13" s="51"/>
@@ -2747,9 +2747,9 @@
       </c>
     </row>
     <row r="14" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A14" s="91"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="93"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="96"/>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
       <c r="F14" s="51"/>
@@ -2777,9 +2777,9 @@
       </c>
     </row>
     <row r="15" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="93"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="96"/>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
@@ -2807,9 +2807,9 @@
       </c>
     </row>
     <row r="16" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A16" s="91"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="93"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="96"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
@@ -2837,9 +2837,9 @@
       </c>
     </row>
     <row r="17" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92"/>
-      <c r="C17" s="93"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="96"/>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
@@ -2867,9 +2867,9 @@
       </c>
     </row>
     <row r="18" spans="1:22" s="53" customFormat="1" ht="28.95" customHeight="1">
-      <c r="A18" s="87"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="89"/>
+      <c r="A18" s="90"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="92"/>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
@@ -2897,9 +2897,9 @@
       </c>
     </row>
     <row r="19" spans="1:22" s="53" customFormat="1" ht="28.2" customHeight="1">
-      <c r="A19" s="87"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="89"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="92"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
@@ -2927,11 +2927,11 @@
       </c>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="80"/>
-      <c r="C20" s="81"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="84"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54">
         <f>SUM(E8:E19)</f>
@@ -3007,11 +3007,11 @@
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="81"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="84"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54">
         <f>E20</f>
@@ -3112,11 +3112,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="D2:V2"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A6:C7"/>
@@ -3133,6 +3128,11 @@
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="D2:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" orientation="landscape" r:id="rId1"/>
@@ -3150,30 +3150,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="19.2" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
     </row>
     <row r="2" spans="1:22" ht="15.6">
       <c r="A2" s="10"/>
@@ -3200,37 +3200,37 @@
       <c r="V2" s="10"/>
     </row>
     <row r="3" spans="1:22" ht="14.4" customHeight="1">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="108" t="s">
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="108"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="108"/>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
     </row>
     <row r="4" spans="1:22" ht="170.4" customHeight="1">
-      <c r="A4" s="107"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
       <c r="D4" s="20" t="s">
         <v>20</v>
       </c>
@@ -3290,11 +3290,11 @@
       </c>
     </row>
     <row r="5" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="100" t="s">
         <v>277</v>
       </c>
-      <c r="B5" s="99"/>
-      <c r="C5" s="100"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="102"/>
       <c r="D5" s="7">
         <v>25</v>
       </c>
@@ -3326,11 +3326,11 @@
       </c>
     </row>
     <row r="6" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="100" t="s">
         <v>278</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="100"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="102"/>
       <c r="D6" s="7">
         <v>92</v>
       </c>
@@ -3362,11 +3362,11 @@
       </c>
     </row>
     <row r="7" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="100" t="s">
         <v>274</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="100"/>
+      <c r="B7" s="101"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="7">
         <v>59</v>
       </c>
@@ -3404,11 +3404,11 @@
       </c>
     </row>
     <row r="8" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A8" s="98" t="s">
+      <c r="A8" s="100" t="s">
         <v>275</v>
       </c>
-      <c r="B8" s="99"/>
-      <c r="C8" s="100"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="102"/>
       <c r="D8" s="7">
         <v>108</v>
       </c>
@@ -3442,11 +3442,11 @@
       </c>
     </row>
     <row r="9" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A9" s="98" t="s">
+      <c r="A9" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="B9" s="99"/>
-      <c r="C9" s="100"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="102"/>
       <c r="D9" s="7">
         <v>108</v>
       </c>
@@ -3482,9 +3482,9 @@
       </c>
     </row>
     <row r="10" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="100"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -3512,9 +3512,9 @@
       </c>
     </row>
     <row r="11" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="100"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="102"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -3542,9 +3542,9 @@
       </c>
     </row>
     <row r="12" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="100"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -3572,9 +3572,9 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="100"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="102"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -3602,9 +3602,9 @@
       </c>
     </row>
     <row r="14" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A14" s="109"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="111"/>
+      <c r="A14" s="103"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="105"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -3632,9 +3632,9 @@
       </c>
     </row>
     <row r="15" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A15" s="109"/>
-      <c r="B15" s="110"/>
-      <c r="C15" s="111"/>
+      <c r="A15" s="103"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -3662,9 +3662,9 @@
       </c>
     </row>
     <row r="16" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A16" s="101"/>
-      <c r="B16" s="102"/>
-      <c r="C16" s="103"/>
+      <c r="A16" s="107"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="109"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -3692,9 +3692,9 @@
       </c>
     </row>
     <row r="17" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A17" s="101"/>
-      <c r="B17" s="102"/>
-      <c r="C17" s="103"/>
+      <c r="A17" s="107"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="109"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -3722,11 +3722,11 @@
       </c>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="105"/>
-      <c r="C18" s="106"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
         <f>SUM(E5:E17)</f>
@@ -3802,11 +3802,11 @@
       </c>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="104" t="s">
+      <c r="A19" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="105"/>
-      <c r="C19" s="106"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
         <f>E18</f>
@@ -3882,11 +3882,11 @@
       </c>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="104" t="s">
+      <c r="A20" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="105"/>
-      <c r="C20" s="106"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="99"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
         <f>SUM(E18,'Осенний сем.'!E20)</f>
@@ -3962,11 +3962,11 @@
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="104" t="s">
+      <c r="A21" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="105"/>
-      <c r="C21" s="106"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="99"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
         <f>SUM(E19,'Осенний сем.'!E21)</f>
@@ -4067,12 +4067,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A16:C16"/>
@@ -4087,6 +4081,12 @@
     <mergeCell ref="A3:C4"/>
     <mergeCell ref="D3:V3"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" orientation="landscape" r:id="rId1"/>
@@ -6197,15 +6197,15 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="19.2" customHeight="1">
-      <c r="A2" s="134" t="s">
+      <c r="A2" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8">
@@ -6849,10 +6849,10 @@
       <c r="H35" s="1"/>
     </row>
     <row r="36" spans="1:8" ht="25.95" customHeight="1">
-      <c r="A36" s="135" t="s">
+      <c r="A36" s="138" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="135"/>
+      <c r="B36" s="138"/>
       <c r="C36" s="2"/>
       <c r="D36" s="5">
         <f>SUM(D35,D30)</f>
@@ -6873,15 +6873,15 @@
       <c r="H36" s="1"/>
     </row>
     <row r="37" spans="1:8" ht="28.95" customHeight="1">
-      <c r="A37" s="133" t="s">
+      <c r="A37" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="133"/>
-      <c r="C37" s="133"/>
-      <c r="D37" s="133"/>
-      <c r="E37" s="133"/>
-      <c r="F37" s="133"/>
-      <c r="G37" s="133"/>
+      <c r="B37" s="136"/>
+      <c r="C37" s="136"/>
+      <c r="D37" s="136"/>
+      <c r="E37" s="136"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="136"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38" spans="1:8" ht="66" customHeight="1">
@@ -6897,10 +6897,10 @@
       <c r="D38" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="136" t="s">
+      <c r="E38" s="133" t="s">
         <v>104</v>
       </c>
-      <c r="F38" s="136"/>
+      <c r="F38" s="133"/>
       <c r="G38" s="17" t="s">
         <v>105</v>
       </c>
@@ -6911,8 +6911,8 @@
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="137"/>
-      <c r="F39" s="138"/>
+      <c r="E39" s="134"/>
+      <c r="F39" s="135"/>
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
     </row>
@@ -6921,8 +6921,8 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="137"/>
-      <c r="F40" s="138"/>
+      <c r="E40" s="134"/>
+      <c r="F40" s="135"/>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
     </row>
@@ -6931,8 +6931,8 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="137"/>
-      <c r="F41" s="138"/>
+      <c r="E41" s="134"/>
+      <c r="F41" s="135"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
     </row>
@@ -6941,8 +6941,8 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="138"/>
+      <c r="E42" s="134"/>
+      <c r="F42" s="135"/>
       <c r="G42" s="2"/>
       <c r="H42" s="1"/>
     </row>
@@ -6978,11 +6978,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -6996,6 +6991,11 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -7014,520 +7014,617 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.95" customHeight="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
     </row>
     <row r="2" spans="1:9" ht="52.2" customHeight="1">
       <c r="A2" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="146" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="148" t="s">
+      <c r="C2" s="146"/>
+      <c r="D2" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="148"/>
+      <c r="E2" s="149"/>
       <c r="F2" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="G2" s="149" t="s">
+      <c r="G2" s="150" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="149"/>
+      <c r="H2" s="150"/>
       <c r="I2" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.95" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="19.95" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="19.95" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="19.95" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="137"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="143"/>
-      <c r="E6" s="144"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="142"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="138"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="135"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" ht="19.95" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="137"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="143"/>
-      <c r="E7" s="144"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="142"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="137"/>
-      <c r="H7" s="138"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="135"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" ht="19.95" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="137"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="143"/>
-      <c r="E8" s="144"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="142"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="137"/>
-      <c r="H8" s="138"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="135"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" ht="19.95" customHeight="1">
       <c r="A9" s="2"/>
-      <c r="B9" s="137"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="143"/>
-      <c r="E9" s="144"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="142"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="138"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="135"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" ht="19.95" customHeight="1">
       <c r="A10" s="2"/>
-      <c r="B10" s="137"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="143"/>
-      <c r="E10" s="144"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="142"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="138"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="135"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="19.95" customHeight="1">
       <c r="A11" s="2"/>
-      <c r="B11" s="137"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="143"/>
-      <c r="E11" s="144"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="142"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="138"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="135"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="19.95" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="137"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="143"/>
-      <c r="E12" s="144"/>
+      <c r="B12" s="134"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="142"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="137"/>
-      <c r="H12" s="138"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="135"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="19.95" customHeight="1">
       <c r="A13" s="2"/>
-      <c r="B13" s="137"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="144"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="142"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="138"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="135"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="19.95" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="B14" s="137"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="144"/>
+      <c r="B14" s="134"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="142"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="137"/>
-      <c r="H14" s="138"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="135"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="19.95" customHeight="1">
       <c r="A15" s="2"/>
-      <c r="B15" s="137"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="144"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="142"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="138"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="135"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="19.95" customHeight="1">
       <c r="A16" s="2"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="19.95" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="108"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="139"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="108"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="19.95" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="108"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="108"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="36" customHeight="1">
-      <c r="A19" s="150" t="s">
+      <c r="A19" s="151" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="150"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="150"/>
-      <c r="I19" s="150"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
+      <c r="H19" s="151"/>
+      <c r="I19" s="151"/>
     </row>
     <row r="20" spans="1:9" ht="54" customHeight="1">
       <c r="A20" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="141" t="s">
+      <c r="B20" s="153" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="142"/>
-      <c r="D20" s="146" t="s">
+      <c r="C20" s="154"/>
+      <c r="D20" s="147" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="147"/>
+      <c r="E20" s="148"/>
       <c r="F20" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="136" t="s">
+      <c r="G20" s="133" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="136"/>
+      <c r="H20" s="133"/>
       <c r="I20" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="19.95" customHeight="1">
       <c r="A21" s="2"/>
-      <c r="B21" s="137"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="138"/>
+      <c r="B21" s="134"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="134"/>
+      <c r="E21" s="135"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="138"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="135"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" ht="19.95" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="137"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="138"/>
+      <c r="B22" s="134"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="135"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="138"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="135"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" ht="19.95" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="137"/>
-      <c r="C23" s="138"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="138"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="135"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="137"/>
-      <c r="H23" s="138"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="135"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" ht="19.95" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="137"/>
-      <c r="C24" s="138"/>
-      <c r="D24" s="137"/>
-      <c r="E24" s="138"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="135"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="137"/>
-      <c r="H24" s="138"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="135"/>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9" ht="19.95" customHeight="1">
       <c r="A25" s="2"/>
-      <c r="B25" s="137"/>
-      <c r="C25" s="138"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="138"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="135"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="138"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="135"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" ht="19.95" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="137"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="137"/>
-      <c r="E26" s="138"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="134"/>
+      <c r="E26" s="135"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="137"/>
-      <c r="H26" s="138"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="135"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" ht="19.95" customHeight="1">
       <c r="A27" s="2"/>
-      <c r="B27" s="137"/>
-      <c r="C27" s="138"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="138"/>
+      <c r="B27" s="134"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="134"/>
+      <c r="E27" s="135"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="138"/>
+      <c r="G27" s="134"/>
+      <c r="H27" s="135"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" ht="19.95" customHeight="1">
       <c r="A28" s="2"/>
-      <c r="B28" s="137"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="138"/>
+      <c r="B28" s="134"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="135"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="138"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="135"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="19.95" customHeight="1">
       <c r="A29" s="2"/>
-      <c r="B29" s="137"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="138"/>
+      <c r="B29" s="134"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="134"/>
+      <c r="E29" s="135"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="138"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="135"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" ht="19.95" customHeight="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="137"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="138"/>
+      <c r="B30" s="134"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="135"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="138"/>
+      <c r="G30" s="134"/>
+      <c r="H30" s="135"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" ht="19.95" customHeight="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="137"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="138"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="134"/>
+      <c r="E31" s="135"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="138"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="135"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" ht="19.95" customHeight="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="137"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="138"/>
+      <c r="B32" s="134"/>
+      <c r="C32" s="135"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="135"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="137"/>
-      <c r="H32" s="138"/>
+      <c r="G32" s="134"/>
+      <c r="H32" s="135"/>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" ht="19.95" customHeight="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="137"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="138"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="135"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="135"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="137"/>
-      <c r="H33" s="138"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="135"/>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9" ht="19.95" customHeight="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="137"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="138"/>
+      <c r="B34" s="134"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="134"/>
+      <c r="E34" s="135"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="138"/>
+      <c r="G34" s="134"/>
+      <c r="H34" s="135"/>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" ht="19.95" customHeight="1">
       <c r="A35" s="2"/>
-      <c r="B35" s="137"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="138"/>
+      <c r="B35" s="134"/>
+      <c r="C35" s="135"/>
+      <c r="D35" s="134"/>
+      <c r="E35" s="135"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="138"/>
+      <c r="G35" s="134"/>
+      <c r="H35" s="135"/>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" ht="24" customHeight="1">
-      <c r="A36" s="133" t="s">
+      <c r="A36" s="136" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="133"/>
-      <c r="C36" s="133"/>
-      <c r="D36" s="133"/>
-      <c r="E36" s="133"/>
-      <c r="F36" s="133"/>
-      <c r="G36" s="133"/>
-      <c r="H36" s="133"/>
-      <c r="I36" s="133"/>
+      <c r="B36" s="136"/>
+      <c r="C36" s="136"/>
+      <c r="D36" s="136"/>
+      <c r="E36" s="136"/>
+      <c r="F36" s="136"/>
+      <c r="G36" s="136"/>
+      <c r="H36" s="136"/>
+      <c r="I36" s="136"/>
     </row>
     <row r="37" spans="1:9" ht="21" customHeight="1">
-      <c r="A37" s="140" t="s">
+      <c r="A37" s="152" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="140"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="140"/>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="140"/>
+      <c r="B37" s="152"/>
+      <c r="C37" s="152"/>
+      <c r="D37" s="152"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="152"/>
+      <c r="H37" s="152"/>
+      <c r="I37" s="152"/>
     </row>
     <row r="38" spans="1:9" ht="35.4" customHeight="1">
-      <c r="A38" s="152" t="s">
+      <c r="A38" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="152"/>
-      <c r="C38" s="152"/>
+      <c r="B38" s="145"/>
+      <c r="C38" s="145"/>
       <c r="D38" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="151" t="s">
+      <c r="E38" s="144" t="s">
         <v>112</v>
       </c>
-      <c r="F38" s="151"/>
-      <c r="G38" s="107" t="s">
+      <c r="F38" s="144"/>
+      <c r="G38" s="110" t="s">
         <v>113</v>
       </c>
-      <c r="H38" s="107"/>
-      <c r="I38" s="107"/>
+      <c r="H38" s="110"/>
+      <c r="I38" s="110"/>
     </row>
     <row r="39" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A39" s="139"/>
-      <c r="B39" s="139"/>
-      <c r="C39" s="139"/>
+      <c r="A39" s="143"/>
+      <c r="B39" s="143"/>
+      <c r="C39" s="143"/>
       <c r="D39" s="3"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="139"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
+      <c r="E39" s="143"/>
+      <c r="F39" s="143"/>
+      <c r="G39" s="143"/>
+      <c r="H39" s="143"/>
+      <c r="I39" s="143"/>
     </row>
     <row r="40" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A40" s="143"/>
-      <c r="B40" s="154"/>
-      <c r="C40" s="144"/>
+      <c r="A40" s="140"/>
+      <c r="B40" s="141"/>
+      <c r="C40" s="142"/>
       <c r="D40" s="3"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="144"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="154"/>
-      <c r="I40" s="144"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="141"/>
+      <c r="I40" s="142"/>
     </row>
     <row r="41" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A41" s="139"/>
-      <c r="B41" s="139"/>
-      <c r="C41" s="139"/>
+      <c r="A41" s="143"/>
+      <c r="B41" s="143"/>
+      <c r="C41" s="143"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="139"/>
-      <c r="H41" s="139"/>
-      <c r="I41" s="139"/>
+      <c r="E41" s="143"/>
+      <c r="F41" s="143"/>
+      <c r="G41" s="143"/>
+      <c r="H41" s="143"/>
+      <c r="I41" s="143"/>
     </row>
     <row r="42" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A42" s="139"/>
-      <c r="B42" s="139"/>
-      <c r="C42" s="139"/>
+      <c r="A42" s="143"/>
+      <c r="B42" s="143"/>
+      <c r="C42" s="143"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="139"/>
+      <c r="E42" s="143"/>
+      <c r="F42" s="143"/>
+      <c r="G42" s="143"/>
+      <c r="H42" s="143"/>
+      <c r="I42" s="143"/>
     </row>
     <row r="43" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A43" s="139"/>
-      <c r="B43" s="139"/>
-      <c r="C43" s="139"/>
+      <c r="A43" s="143"/>
+      <c r="B43" s="143"/>
+      <c r="C43" s="143"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
-      <c r="G43" s="139"/>
-      <c r="H43" s="139"/>
-      <c r="I43" s="139"/>
+      <c r="E43" s="143"/>
+      <c r="F43" s="143"/>
+      <c r="G43" s="143"/>
+      <c r="H43" s="143"/>
+      <c r="I43" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="121">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D29:E29"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B13:C13"/>
@@ -7552,103 +7649,6 @@
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
@@ -7672,71 +7672,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="155" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="168"/>
-      <c r="I1" s="168"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
     </row>
     <row r="2" spans="1:10" ht="20.399999999999999" customHeight="1">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
     </row>
     <row r="3" spans="1:10" ht="15.6">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="170" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="155"/>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="170"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="170"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="170"/>
+      <c r="I3" s="170"/>
     </row>
     <row r="4" spans="1:10" ht="15.6">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="172" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="57">
-        <v>0.43</v>
-      </c>
+      <c r="B4" s="172"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="58" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="156"/>
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156"/>
-      <c r="I5" s="156"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
     </row>
     <row r="6" spans="1:10" ht="29.4" customHeight="1">
       <c r="A6" s="162" t="s">
@@ -7758,26 +7756,26 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.6">
-      <c r="A7" s="163" t="s">
+      <c r="A7" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="163"/>
-      <c r="C7" s="163"/>
-      <c r="D7" s="163"/>
-      <c r="E7" s="163"/>
-      <c r="F7" s="163"/>
+      <c r="B7" s="167"/>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="167"/>
       <c r="G7" s="61"/>
       <c r="H7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="15.6">
-      <c r="A8" s="163" t="s">
+      <c r="A8" s="167" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="163"/>
-      <c r="C8" s="163"/>
-      <c r="D8" s="163"/>
-      <c r="E8" s="163"/>
-      <c r="F8" s="163"/>
+      <c r="B8" s="167"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
       <c r="G8" s="61"/>
       <c r="H8" s="61"/>
       <c r="I8" s="60" t="s">
@@ -7785,14 +7783,14 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A9" s="164" t="s">
+      <c r="A9" s="168" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="164"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
+      <c r="B9" s="168"/>
+      <c r="C9" s="168"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="168"/>
+      <c r="F9" s="168"/>
       <c r="G9" s="61"/>
       <c r="H9" s="61"/>
       <c r="I9" s="62" t="s">
@@ -7800,14 +7798,14 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6">
-      <c r="A10" s="163" t="s">
+      <c r="A10" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="163"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="163"/>
-      <c r="F10" s="163"/>
+      <c r="B10" s="167"/>
+      <c r="C10" s="167"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
       <c r="G10" s="61"/>
       <c r="H10" s="61"/>
       <c r="I10" s="63">
@@ -7817,14 +7815,14 @@
       <c r="J10" s="69"/>
     </row>
     <row r="11" spans="1:10" ht="23.4" customHeight="1">
-      <c r="A11" s="165" t="s">
+      <c r="A11" s="169" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="165"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="165"/>
+      <c r="B11" s="169"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="169"/>
+      <c r="F11" s="169"/>
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
       <c r="I11" s="63" t="s">
@@ -7832,111 +7830,111 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="41.4" customHeight="1">
-      <c r="A12" s="158"/>
-      <c r="B12" s="158"/>
-      <c r="C12" s="158"/>
-      <c r="D12" s="158"/>
-      <c r="E12" s="158"/>
-      <c r="F12" s="158"/>
-      <c r="G12" s="158"/>
-      <c r="H12" s="158"/>
-      <c r="I12" s="158"/>
+      <c r="A12" s="173"/>
+      <c r="B12" s="173"/>
+      <c r="C12" s="173"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="173"/>
     </row>
     <row r="13" spans="1:10" ht="31.95" customHeight="1">
-      <c r="A13" s="159" t="s">
+      <c r="A13" s="165" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="160"/>
-      <c r="C13" s="160"/>
-      <c r="D13" s="160"/>
-      <c r="E13" s="160"/>
-      <c r="F13" s="160"/>
-      <c r="G13" s="160"/>
-      <c r="H13" s="160"/>
-      <c r="I13" s="160"/>
+      <c r="B13" s="166"/>
+      <c r="C13" s="166"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="166"/>
     </row>
     <row r="14" spans="1:10" ht="29.4" customHeight="1">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="164" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="161"/>
-      <c r="C14" s="161"/>
-      <c r="D14" s="161"/>
-      <c r="E14" s="161"/>
-      <c r="F14" s="161"/>
-      <c r="G14" s="167" t="s">
+      <c r="B14" s="164"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="164"/>
+      <c r="E14" s="164"/>
+      <c r="F14" s="164"/>
+      <c r="G14" s="163" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="161"/>
-      <c r="I14" s="161"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="164"/>
     </row>
     <row r="15" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A15" s="166"/>
-      <c r="B15" s="166"/>
-      <c r="C15" s="166"/>
-      <c r="D15" s="166"/>
-      <c r="E15" s="166"/>
-      <c r="F15" s="166"/>
-      <c r="G15" s="166"/>
-      <c r="H15" s="166"/>
-      <c r="I15" s="166"/>
+      <c r="A15" s="158"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+      <c r="F15" s="158"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="158"/>
     </row>
     <row r="16" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A16" s="166"/>
-      <c r="B16" s="166"/>
-      <c r="C16" s="166"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="166"/>
-      <c r="F16" s="166"/>
-      <c r="G16" s="166"/>
-      <c r="H16" s="166"/>
-      <c r="I16" s="166"/>
+      <c r="A16" s="158"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
     </row>
     <row r="17" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A17" s="166"/>
-      <c r="B17" s="166"/>
-      <c r="C17" s="166"/>
-      <c r="D17" s="166"/>
-      <c r="E17" s="166"/>
-      <c r="F17" s="166"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="166"/>
-      <c r="I17" s="166"/>
+      <c r="A17" s="158"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="158"/>
+      <c r="G17" s="158"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="158"/>
     </row>
     <row r="18" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A18" s="166"/>
-      <c r="B18" s="166"/>
-      <c r="C18" s="166"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="166"/>
-      <c r="F18" s="166"/>
-      <c r="G18" s="166"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="166"/>
+      <c r="A18" s="158"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="158"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="158"/>
     </row>
     <row r="19" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A19" s="166"/>
-      <c r="B19" s="166"/>
-      <c r="C19" s="166"/>
-      <c r="D19" s="166"/>
-      <c r="E19" s="166"/>
-      <c r="F19" s="166"/>
-      <c r="G19" s="166"/>
-      <c r="H19" s="166"/>
-      <c r="I19" s="166"/>
+      <c r="A19" s="158"/>
+      <c r="B19" s="158"/>
+      <c r="C19" s="158"/>
+      <c r="D19" s="158"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="158"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="158"/>
+      <c r="I19" s="158"/>
     </row>
     <row r="20" spans="1:9" ht="33.6" customHeight="1">
-      <c r="A20" s="172" t="s">
+      <c r="A20" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="173"/>
-      <c r="C20" s="173"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="173"/>
+      <c r="B20" s="161"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="161"/>
+      <c r="H20" s="161"/>
+      <c r="I20" s="161"/>
     </row>
     <row r="21" spans="1:9" ht="21" customHeight="1">
       <c r="A21" s="65" t="s">
@@ -7955,139 +7953,164 @@
     </row>
     <row r="22" spans="1:9" ht="16.95" customHeight="1">
       <c r="A22" s="66"/>
-      <c r="B22" s="166"/>
-      <c r="C22" s="166"/>
-      <c r="D22" s="166"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="166"/>
+      <c r="B22" s="158"/>
+      <c r="C22" s="158"/>
+      <c r="D22" s="158"/>
+      <c r="E22" s="158"/>
+      <c r="F22" s="158"/>
+      <c r="G22" s="158"/>
+      <c r="H22" s="158"/>
+      <c r="I22" s="158"/>
     </row>
     <row r="23" spans="1:9" ht="16.95" customHeight="1">
       <c r="A23" s="66"/>
-      <c r="B23" s="166"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="166"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="166"/>
-      <c r="G23" s="166"/>
-      <c r="H23" s="166"/>
-      <c r="I23" s="166"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="158"/>
+      <c r="E23" s="158"/>
+      <c r="F23" s="158"/>
+      <c r="G23" s="158"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="158"/>
     </row>
     <row r="24" spans="1:9" ht="16.95" customHeight="1">
       <c r="A24" s="66"/>
-      <c r="B24" s="166"/>
-      <c r="C24" s="166"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="166"/>
-      <c r="G24" s="166"/>
-      <c r="H24" s="166"/>
-      <c r="I24" s="166"/>
+      <c r="B24" s="158"/>
+      <c r="C24" s="158"/>
+      <c r="D24" s="158"/>
+      <c r="E24" s="158"/>
+      <c r="F24" s="158"/>
+      <c r="G24" s="158"/>
+      <c r="H24" s="158"/>
+      <c r="I24" s="158"/>
     </row>
     <row r="25" spans="1:9" ht="16.95" customHeight="1">
       <c r="A25" s="66"/>
-      <c r="B25" s="166"/>
-      <c r="C25" s="166"/>
-      <c r="D25" s="166"/>
-      <c r="E25" s="166"/>
-      <c r="F25" s="166"/>
-      <c r="G25" s="166"/>
-      <c r="H25" s="166"/>
-      <c r="I25" s="166"/>
+      <c r="B25" s="158"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="158"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="158"/>
     </row>
     <row r="26" spans="1:9" ht="16.95" customHeight="1">
       <c r="A26" s="66"/>
-      <c r="B26" s="166"/>
-      <c r="C26" s="166"/>
-      <c r="D26" s="166"/>
-      <c r="E26" s="166"/>
-      <c r="F26" s="166"/>
-      <c r="G26" s="166"/>
-      <c r="H26" s="166"/>
-      <c r="I26" s="166"/>
+      <c r="B26" s="158"/>
+      <c r="C26" s="158"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="158"/>
+      <c r="G26" s="158"/>
+      <c r="H26" s="158"/>
+      <c r="I26" s="158"/>
     </row>
     <row r="27" spans="1:9" ht="16.95" customHeight="1">
       <c r="A27" s="66"/>
-      <c r="B27" s="166"/>
-      <c r="C27" s="166"/>
-      <c r="D27" s="166"/>
-      <c r="E27" s="166"/>
-      <c r="F27" s="166"/>
-      <c r="G27" s="166"/>
-      <c r="H27" s="166"/>
-      <c r="I27" s="166"/>
+      <c r="B27" s="158"/>
+      <c r="C27" s="158"/>
+      <c r="D27" s="158"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="158"/>
+      <c r="G27" s="158"/>
+      <c r="H27" s="158"/>
+      <c r="I27" s="158"/>
     </row>
     <row r="28" spans="1:9" ht="16.95" customHeight="1">
       <c r="A28" s="66"/>
-      <c r="B28" s="166"/>
-      <c r="C28" s="166"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="166"/>
-      <c r="F28" s="166"/>
-      <c r="G28" s="166"/>
-      <c r="H28" s="166"/>
-      <c r="I28" s="166"/>
+      <c r="B28" s="158"/>
+      <c r="C28" s="158"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="158"/>
+      <c r="G28" s="158"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="158"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="171"/>
-      <c r="B29" s="171"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="171"/>
-      <c r="I29" s="171"/>
+      <c r="A29" s="159"/>
+      <c r="B29" s="159"/>
+      <c r="C29" s="159"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="159"/>
+      <c r="F29" s="159"/>
+      <c r="G29" s="159"/>
+      <c r="H29" s="159"/>
+      <c r="I29" s="159"/>
     </row>
     <row r="30" spans="1:9" ht="60" customHeight="1">
-      <c r="A30" s="169" t="s">
+      <c r="A30" s="156" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="169"/>
-      <c r="C30" s="169"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="169" t="s">
+      <c r="B30" s="156"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="156" t="s">
         <v>279</v>
       </c>
-      <c r="G30" s="169"/>
-      <c r="H30" s="169"/>
+      <c r="G30" s="156"/>
+      <c r="H30" s="156"/>
       <c r="I30" s="67"/>
     </row>
     <row r="31" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A31" s="170" t="s">
+      <c r="A31" s="157" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="170"/>
-      <c r="C31" s="170"/>
-      <c r="D31" s="170"/>
-      <c r="E31" s="170"/>
-      <c r="F31" s="170" t="s">
+      <c r="B31" s="157"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="157"/>
+      <c r="F31" s="157" t="s">
         <v>267</v>
       </c>
-      <c r="G31" s="170"/>
-      <c r="H31" s="170"/>
+      <c r="G31" s="157"/>
+      <c r="H31" s="157"/>
       <c r="I31" s="68"/>
     </row>
     <row r="32" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A32" s="169" t="s">
+      <c r="A32" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="169"/>
-      <c r="C32" s="169"/>
-      <c r="D32" s="169"/>
-      <c r="E32" s="169"/>
-      <c r="F32" s="170" t="s">
+      <c r="B32" s="156"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="157" t="s">
         <v>81</v>
       </c>
-      <c r="G32" s="170"/>
-      <c r="H32" s="170"/>
+      <c r="G32" s="157"/>
+      <c r="H32" s="157"/>
       <c r="I32" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G16:I16"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A31:E31"/>
@@ -8104,31 +8127,6 @@
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:I12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>

--- a/Templates/IndividualPlanTemplate.xlsx
+++ b/Templates/IndividualPlanTemplate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\8semestr\vkrpolina\departmentLoadApp\DepartmentLoadApp\Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CA553E-012C-4BD3-AA8A-3F8D34D04DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="8"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Титул" sheetId="1" r:id="rId1"/>
@@ -20,17 +26,31 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Титул!$A$1:$J$25</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="281">
   <si>
     <t>МИНИСТЕРСТВО НАУКИ И ВЫСШЕГО ОБРАЗОВАНИЯ РОССИЙСКОЙ ФЕДЕРАЦИИ</t>
   </si>
@@ -289,18 +309,8 @@
     <t>)</t>
   </si>
   <si>
-    <t>заполните пункты</t>
-  </si>
-  <si>
-    <t>часов</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 План повышения квалификации за учебный год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-4 так, 
-чтобы добрать </t>
   </si>
   <si>
     <t>Подготовка к лекциям</t>
@@ -934,11 +944,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1221,7 +1231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1353,9 +1363,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1363,18 +1370,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1388,6 +1383,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1699,6 +1712,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2006,266 +2022,266 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-    </row>
-    <row r="2" spans="1:10" ht="27" customHeight="1">
-      <c r="A2" s="76" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+    </row>
+    <row r="2" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-    </row>
-    <row r="3" spans="1:10" ht="27" customHeight="1">
-      <c r="A3" s="76" t="s">
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+    </row>
+    <row r="3" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-    </row>
-    <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="77" t="s">
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+    </row>
+    <row r="4" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-    </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1"/>
-    <row r="6" spans="1:10" ht="30" customHeight="1"/>
-    <row r="7" spans="1:10" ht="30" customHeight="1"/>
-    <row r="8" spans="1:10" ht="30" customHeight="1"/>
-    <row r="9" spans="1:10" ht="30" customHeight="1"/>
-    <row r="10" spans="1:10" ht="39.6" customHeight="1">
-      <c r="A10" s="74" t="s">
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-    </row>
-    <row r="11" spans="1:10" ht="40.200000000000003" customHeight="1">
-      <c r="A11" s="74" t="s">
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+    </row>
+    <row r="11" spans="1:10" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
-    </row>
-    <row r="12" spans="1:10" ht="40.200000000000003" customHeight="1">
-      <c r="A12" s="75" t="s">
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+    </row>
+    <row r="12" spans="1:10" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="75"/>
-    </row>
-    <row r="13" spans="1:10" ht="28.95" customHeight="1"/>
-    <row r="14" spans="1:10" ht="34.200000000000003" customHeight="1"/>
-    <row r="15" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A15" s="70" t="s">
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="71" t="s">
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-    </row>
-    <row r="16" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A16" s="70" t="s">
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+    </row>
+    <row r="16" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="72" t="s">
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="75" t="s">
+        <v>265</v>
+      </c>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="76" t="s">
+        <v>266</v>
+      </c>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="76"/>
+    </row>
+    <row r="18" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="76" t="s">
+        <v>267</v>
+      </c>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+    </row>
+    <row r="19" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="81" t="s">
         <v>268</v>
       </c>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A17" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="73" t="s">
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+    </row>
+    <row r="20" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="76" t="s">
         <v>269</v>
       </c>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-    </row>
-    <row r="18" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A18" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="73" t="s">
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="76"/>
+    </row>
+    <row r="21" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="81">
+        <v>1994</v>
+      </c>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="81"/>
+    </row>
+    <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="73"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="76" t="s">
         <v>270</v>
       </c>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
-    </row>
-    <row r="19" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A19" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="78" t="s">
-        <v>271</v>
-      </c>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-    </row>
-    <row r="20" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A20" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="73" t="s">
-        <v>272</v>
-      </c>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-    </row>
-    <row r="21" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A21" s="70" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="78">
-        <v>1994</v>
-      </c>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-    </row>
-    <row r="22" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A22" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="73" t="s">
-        <v>273</v>
-      </c>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-    </row>
-    <row r="23" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A23" s="70" t="s">
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+    </row>
+    <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -2301,9 +2317,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="48"/>
     <col min="3" max="3" width="55" style="48" customWidth="1"/>
@@ -2312,12 +2328,12 @@
     <col min="23" max="16384" width="9.109375" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.6">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
       <c r="D1" s="46"/>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2340,35 +2356,35 @@
       <c r="U1" s="46"/>
       <c r="V1" s="46"/>
     </row>
-    <row r="2" spans="1:22" ht="19.2" customHeight="1">
-      <c r="A2" s="79" t="s">
-        <v>266</v>
-      </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="81" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-    </row>
-    <row r="3" spans="1:22" ht="19.2" customHeight="1">
+    <row r="2" spans="1:22" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="82" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="84" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+    </row>
+    <row r="3" spans="1:22" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="46"/>
       <c r="B3" s="46"/>
       <c r="C3" s="46"/>
@@ -2377,14 +2393,14 @@
       <c r="F3" s="46"/>
       <c r="G3" s="46"/>
       <c r="H3" s="46"/>
-      <c r="I3" s="80" t="s">
+      <c r="I3" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
       <c r="O3" s="46"/>
       <c r="P3" s="46"/>
       <c r="Q3" s="46"/>
@@ -2394,12 +2410,12 @@
       <c r="U3" s="46"/>
       <c r="V3" s="46"/>
     </row>
-    <row r="4" spans="1:22" ht="18.600000000000001" customHeight="1">
-      <c r="A4" s="79" t="s">
-        <v>281</v>
-      </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
+    <row r="4" spans="1:22" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
       <c r="D4" s="46"/>
       <c r="E4" s="46"/>
       <c r="F4" s="46"/>
@@ -2420,7 +2436,7 @@
       <c r="U4" s="46"/>
       <c r="V4" s="46"/>
     </row>
-    <row r="5" spans="1:22" ht="15.6">
+    <row r="5" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="46"/>
       <c r="B5" s="46"/>
       <c r="C5" s="46"/>
@@ -2444,38 +2460,38 @@
       <c r="U5" s="46"/>
       <c r="V5" s="46"/>
     </row>
-    <row r="6" spans="1:22" ht="14.4" customHeight="1">
-      <c r="A6" s="85" t="s">
+    <row r="6" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="86" t="s">
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
-      <c r="P6" s="86"/>
-      <c r="Q6" s="86"/>
-      <c r="R6" s="86"/>
-      <c r="S6" s="86"/>
-      <c r="T6" s="86"/>
-      <c r="U6" s="86"/>
-      <c r="V6" s="86"/>
-    </row>
-    <row r="7" spans="1:22" ht="147" customHeight="1">
-      <c r="A7" s="85"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="89"/>
+      <c r="N6" s="89"/>
+      <c r="O6" s="89"/>
+      <c r="P6" s="89"/>
+      <c r="Q6" s="89"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="89"/>
+      <c r="T6" s="89"/>
+      <c r="U6" s="89"/>
+      <c r="V6" s="89"/>
+    </row>
+    <row r="7" spans="1:22" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="88"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="88"/>
       <c r="D7" s="49" t="s">
         <v>20</v>
       </c>
@@ -2483,7 +2499,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>25</v>
@@ -2510,10 +2526,10 @@
         <v>32</v>
       </c>
       <c r="O7" s="49" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q7" s="49" t="s">
         <v>33</v>
@@ -2534,12 +2550,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A8" s="87" t="s">
-        <v>274</v>
-      </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="89"/>
+    <row r="8" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="90" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="91"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="51">
         <v>59</v>
       </c>
@@ -2576,12 +2592,12 @@
         <v>61.400000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A9" s="93" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="89"/>
+    <row r="9" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="96" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
       <c r="D9" s="51">
         <v>108</v>
       </c>
@@ -2614,12 +2630,12 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A10" s="93" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
+    <row r="10" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="96" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="91"/>
+      <c r="C10" s="92"/>
       <c r="D10" s="51">
         <v>108</v>
       </c>
@@ -2656,10 +2672,10 @@
         <v>73.2</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
+    <row r="11" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="96"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
       <c r="F11" s="51"/>
@@ -2686,10 +2702,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="89"/>
+    <row r="12" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="96"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="92"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
       <c r="F12" s="51"/>
@@ -2716,10 +2732,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="88"/>
-      <c r="C13" s="89"/>
+    <row r="13" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="96"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="92"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
       <c r="F13" s="51"/>
@@ -2746,10 +2762,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
+    <row r="14" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="97"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
       <c r="F14" s="51"/>
@@ -2776,10 +2792,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="96"/>
+    <row r="15" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="97"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="99"/>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
       <c r="F15" s="51"/>
@@ -2806,10 +2822,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="96"/>
+    <row r="16" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="97"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="99"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
       <c r="F16" s="51"/>
@@ -2836,10 +2852,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="96"/>
+    <row r="17" spans="1:22" s="53" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="97"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="99"/>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
@@ -2866,10 +2882,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="53" customFormat="1" ht="28.95" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="92"/>
+    <row r="18" spans="1:22" s="53" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="95"/>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
@@ -2896,10 +2912,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="53" customFormat="1" ht="28.2" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="92"/>
+    <row r="19" spans="1:22" s="53" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="93"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="95"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
       <c r="F19" s="51"/>
@@ -2926,12 +2942,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
-      <c r="A20" s="82" t="s">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="84"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54">
         <f>SUM(E8:E19)</f>
@@ -3006,12 +3022,12 @@
         <v>159.80000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
-      <c r="A21" s="82" t="s">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="84"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54">
         <f>E20</f>
@@ -3086,7 +3102,7 @@
         <v>159.80000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="56"/>
       <c r="B22" s="56"/>
       <c r="C22" s="56"/>
@@ -3140,42 +3156,42 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="52.5546875" customWidth="1"/>
     <col min="4" max="20" width="5.6640625" customWidth="1"/>
     <col min="21" max="22" width="6.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="19.2" customHeight="1">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:22" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-    </row>
-    <row r="2" spans="1:22" ht="15.6">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+    </row>
+    <row r="2" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -3199,38 +3215,38 @@
       <c r="U2" s="10"/>
       <c r="V2" s="10"/>
     </row>
-    <row r="3" spans="1:22" ht="14.4" customHeight="1">
-      <c r="A3" s="110" t="s">
+    <row r="3" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="111" t="s">
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-    </row>
-    <row r="4" spans="1:22" ht="170.4" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="114"/>
+      <c r="O3" s="114"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
+      <c r="R3" s="114"/>
+      <c r="S3" s="114"/>
+      <c r="T3" s="114"/>
+      <c r="U3" s="114"/>
+      <c r="V3" s="114"/>
+    </row>
+    <row r="4" spans="1:22" ht="170.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
       <c r="D4" s="20" t="s">
         <v>20</v>
       </c>
@@ -3265,10 +3281,10 @@
         <v>32</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q4" s="20" t="s">
         <v>33</v>
@@ -3289,12 +3305,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A5" s="100" t="s">
-        <v>277</v>
-      </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="102"/>
+    <row r="5" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="103" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="104"/>
+      <c r="C5" s="105"/>
       <c r="D5" s="7">
         <v>25</v>
       </c>
@@ -3325,12 +3341,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A6" s="100" t="s">
-        <v>278</v>
-      </c>
-      <c r="B6" s="101"/>
-      <c r="C6" s="102"/>
+    <row r="6" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="103" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="104"/>
+      <c r="C6" s="105"/>
       <c r="D6" s="7">
         <v>92</v>
       </c>
@@ -3361,12 +3377,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A7" s="100" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="102"/>
+    <row r="7" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="103" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="104"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="7">
         <v>59</v>
       </c>
@@ -3403,12 +3419,12 @@
         <v>103.3</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A8" s="100" t="s">
-        <v>275</v>
-      </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="102"/>
+    <row r="8" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
       <c r="D8" s="7">
         <v>108</v>
       </c>
@@ -3441,12 +3457,12 @@
         <v>43.599999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A9" s="100" t="s">
-        <v>276</v>
-      </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="102"/>
+    <row r="9" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="103" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" s="104"/>
+      <c r="C9" s="105"/>
       <c r="D9" s="7">
         <v>108</v>
       </c>
@@ -3481,10 +3497,10 @@
         <v>59.599999999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="102"/>
+    <row r="10" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="103"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="105"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -3511,10 +3527,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A11" s="100"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="102"/>
+    <row r="11" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="103"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="105"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -3541,10 +3557,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="102"/>
+    <row r="12" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="103"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="105"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -3571,10 +3587,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A13" s="100"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
+    <row r="13" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="103"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="105"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -3601,10 +3617,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A14" s="103"/>
-      <c r="B14" s="104"/>
-      <c r="C14" s="105"/>
+    <row r="14" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="106"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="108"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -3631,10 +3647,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A15" s="103"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="105"/>
+    <row r="15" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="106"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="108"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -3661,10 +3677,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A16" s="107"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="109"/>
+    <row r="16" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="110"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -3691,10 +3707,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1">
-      <c r="A17" s="107"/>
-      <c r="B17" s="108"/>
-      <c r="C17" s="109"/>
+    <row r="17" spans="1:22" s="9" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="110"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -3721,12 +3737,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
-      <c r="A18" s="97" t="s">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="98"/>
-      <c r="C18" s="99"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="102"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5">
         <f>SUM(E5:E17)</f>
@@ -3801,12 +3817,12 @@
         <v>210.5</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
-      <c r="A19" s="97" t="s">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="98"/>
-      <c r="C19" s="99"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="102"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5">
         <f>E18</f>
@@ -3881,12 +3897,12 @@
         <v>210.5</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
-      <c r="A20" s="97" t="s">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="98"/>
-      <c r="C20" s="99"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="102"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5">
         <f>SUM(E18,'Осенний сем.'!E20)</f>
@@ -3961,12 +3977,12 @@
         <v>370.3</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
-      <c r="A21" s="97" t="s">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="99"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="102"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5">
         <f>SUM(E19,'Осенний сем.'!E21)</f>
@@ -4041,7 +4057,7 @@
         <v>370.3</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4094,71 +4110,71 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H67"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.44140625" customWidth="1"/>
     <col min="3" max="3" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="112" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.6">
-      <c r="A2" s="113" t="s">
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="119"/>
-      <c r="B3" s="118" t="s">
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="122"/>
+      <c r="B3" s="121" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="118" t="s">
+      <c r="C3" s="121" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="117" t="s">
+      <c r="D3" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117" t="s">
+      <c r="E3" s="120"/>
+      <c r="F3" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="117"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="119"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="117" t="s">
+      <c r="G3" s="120"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="122"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="117"/>
-    </row>
-    <row r="5" spans="1:8" ht="20.399999999999999">
-      <c r="A5" s="119"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
+      <c r="G4" s="120"/>
+    </row>
+    <row r="5" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="122"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
       <c r="D5" s="34" t="s">
         <v>49</v>
       </c>
@@ -4172,7 +4188,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>1</v>
       </c>
@@ -4195,365 +4211,365 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25.95" customHeight="1">
-      <c r="A7" s="120" t="s">
+    <row r="7" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-    </row>
-    <row r="8" spans="1:8" ht="57" customHeight="1">
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+    </row>
+    <row r="8" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6">
+        <v>117</v>
+      </c>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65">
         <f>D8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6">
+      <c r="F8" s="65"/>
+      <c r="G8" s="65">
         <f>F8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+        <v>118</v>
+      </c>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="26.4">
+    <row r="10" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
         <v>56</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="39.6">
+    <row r="11" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+        <v>126</v>
+      </c>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="26.4">
+    <row r="15" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65">
+        <f t="shared" ref="E17:E23" si="0">D17</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65">
+        <f t="shared" ref="G17:G23" si="1">F17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C18" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" ht="13.95" customHeight="1">
-      <c r="A16" s="37" t="s">
+      <c r="D18" s="65"/>
+      <c r="E18" s="65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" ht="52.8">
-      <c r="A17" s="37" t="s">
+      <c r="B19" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B20" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6">
-        <f t="shared" ref="E17:E23" si="0">D17</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6">
-        <f t="shared" ref="G17:G23" si="1">F17</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" ht="26.4">
-      <c r="A18" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6">
+      <c r="C21" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6">
+      <c r="F21" s="65"/>
+      <c r="G21" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" ht="26.4">
-      <c r="A19" s="37" t="s">
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="B19" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6">
+      <c r="B22" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6">
+      <c r="F22" s="65"/>
+      <c r="G22" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" ht="26.4">
-      <c r="A20" s="37" t="s">
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6">
+      <c r="B23" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6">
+      <c r="F23" s="65"/>
+      <c r="G23" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" ht="55.2" customHeight="1">
-      <c r="A22" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" ht="26.4">
-      <c r="A23" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="5">
+      <c r="D24" s="66">
         <f>SUM(D9:D23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="66">
         <f>SUM(E9:E23)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="66">
         <f>SUM(F9:F23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="66">
         <f>SUM(G9:G23)</f>
         <v>0</v>
       </c>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="121" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="79.8">
+    <row r="26" spans="1:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6">
@@ -4567,15 +4583,15 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="26.4">
+    <row r="27" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6">
@@ -4589,7 +4605,7 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="5" t="s">
         <v>62</v>
@@ -4613,27 +4629,27 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="114" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="115"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="116"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="117" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="118"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="118"/>
+      <c r="G29" s="119"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" ht="27">
+    <row r="30" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A30" s="37" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B30" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="40" t="s">
         <v>158</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>161</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6">
@@ -4647,15 +4663,15 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="27">
+    <row r="31" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="37" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B31" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="40" t="s">
         <v>159</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>162</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6">
@@ -4669,15 +4685,15 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="37" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B32" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="40" t="s">
         <v>160</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>163</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -4688,15 +4704,15 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="27">
+    <row r="33" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A33" s="37" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6">
@@ -4710,15 +4726,15 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" ht="40.200000000000003">
+    <row r="34" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A34" s="37" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6">
@@ -4731,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="5" t="s">
         <v>62</v>
@@ -4755,7 +4771,7 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -4765,7 +4781,7 @@
       <c r="G36" s="28"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="27"/>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
@@ -4775,7 +4791,7 @@
       <c r="G37" s="27"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="27"/>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>
@@ -4785,7 +4801,7 @@
       <c r="G38" s="27"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -4795,7 +4811,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="28"/>
       <c r="C40" s="1"/>
@@ -4805,7 +4821,7 @@
       <c r="G40" s="29"/>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="28"/>
       <c r="B41" s="28"/>
       <c r="C41" s="1"/>
@@ -4815,7 +4831,7 @@
       <c r="G41" s="29"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -4825,7 +4841,7 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -4835,7 +4851,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -4845,7 +4861,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -4855,7 +4871,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -4865,7 +4881,7 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -4875,7 +4891,7 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -4885,7 +4901,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -4895,7 +4911,7 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -4905,7 +4921,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -4915,7 +4931,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -4925,7 +4941,7 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -4935,7 +4951,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -4945,7 +4961,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -4955,7 +4971,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -4965,7 +4981,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -4975,7 +4991,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -4985,7 +5001,7 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -4995,7 +5011,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -5005,7 +5021,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -5015,7 +5031,7 @@
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -5025,7 +5041,7 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -5035,7 +5051,7 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -5045,7 +5061,7 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -5055,7 +5071,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -5065,7 +5081,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -5100,34 +5116,34 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.44140625" customWidth="1"/>
     <col min="3" max="3" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="124"/>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="127"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="40.200000000000003">
+    <row r="2" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="30" t="s">
         <v>172</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>175</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="43">
@@ -5141,15 +5157,15 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="27">
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B3" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="30" t="s">
         <v>173</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>176</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="43">
@@ -5163,15 +5179,15 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="27">
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B4" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="30" t="s">
         <v>174</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>177</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="43">
@@ -5185,7 +5201,7 @@
       </c>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="4" t="s">
         <v>62</v>
@@ -5209,11 +5225,11 @@
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="125" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="125"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="128" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="128"/>
       <c r="C6" s="2"/>
       <c r="D6" s="5">
         <f xml:space="preserve"> SUM(D5,УМР!D35,УМР!D28,УМР!D24)</f>
@@ -5233,7 +5249,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -5243,7 +5259,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -5253,7 +5269,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -5263,7 +5279,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -5273,7 +5289,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -5283,7 +5299,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -5293,7 +5309,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -5303,7 +5319,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -5313,7 +5329,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -5323,7 +5339,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -5333,7 +5349,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -5343,7 +5359,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -5353,7 +5369,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -5363,7 +5379,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5373,7 +5389,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -5383,7 +5399,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5393,7 +5409,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -5403,7 +5419,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5413,7 +5429,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5423,7 +5439,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5433,7 +5449,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5443,7 +5459,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5453,7 +5469,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5463,7 +5479,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5473,7 +5489,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5483,7 +5499,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5505,72 +5521,72 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" customWidth="1"/>
     <col min="2" max="2" width="36.88671875" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="128"/>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-    </row>
-    <row r="2" spans="1:8" ht="16.2">
-      <c r="A2" s="129" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="131"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+    </row>
+    <row r="2" spans="1:8" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A2" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="130"/>
-      <c r="B3" s="131" t="s">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="133"/>
+      <c r="B3" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="131" t="s">
+      <c r="C3" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="132" t="s">
+      <c r="D3" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132" t="s">
+      <c r="E3" s="135"/>
+      <c r="F3" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="132"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="132" t="s">
+      <c r="G3" s="135"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132" t="s">
+      <c r="E4" s="135"/>
+      <c r="F4" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="132"/>
-    </row>
-    <row r="5" spans="1:8" ht="20.399999999999999">
-      <c r="A5" s="130"/>
-      <c r="B5" s="131"/>
-      <c r="C5" s="131"/>
+      <c r="G4" s="135"/>
+    </row>
+    <row r="5" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="133"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
       <c r="D5" s="15" t="s">
         <v>49</v>
       </c>
@@ -5584,7 +5600,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5607,26 +5623,26 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="20.399999999999999" customHeight="1">
-      <c r="A7" s="126" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-    </row>
-    <row r="8" spans="1:8" ht="22.2" customHeight="1">
+    <row r="7" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="129" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+    </row>
+    <row r="8" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
@@ -5640,15 +5656,15 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" ht="27.6" customHeight="1">
+    <row r="9" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6">
@@ -5662,15 +5678,15 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="28.95" customHeight="1">
+    <row r="10" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6">
@@ -5684,15 +5700,15 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="43.2" customHeight="1">
+    <row r="11" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6">
@@ -5706,15 +5722,15 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="28.95" customHeight="1">
+    <row r="12" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
@@ -5728,15 +5744,15 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="43.2" customHeight="1">
+    <row r="13" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
@@ -5750,15 +5766,15 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6">
@@ -5772,12 +5788,12 @@
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
@@ -5791,12 +5807,12 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6">
@@ -5810,12 +5826,12 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
@@ -5829,12 +5845,12 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="29.4" customHeight="1">
+    <row r="18" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6">
@@ -5848,15 +5864,15 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6">
@@ -5870,15 +5886,15 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="28.95" customHeight="1">
+    <row r="20" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6">
@@ -5892,15 +5908,15 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="27.6" customHeight="1">
+    <row r="21" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6">
@@ -5914,15 +5930,15 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="27.6" customHeight="1">
+    <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6">
@@ -5936,7 +5952,7 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="4" t="s">
         <v>62</v>
@@ -5960,27 +5976,27 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1">
-      <c r="A24" s="127" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="130" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="130"/>
+      <c r="C24" s="130"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="41.4" customHeight="1">
+    <row r="25" spans="1:8" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6">
@@ -5994,15 +6010,15 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="27" customHeight="1">
+    <row r="26" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6">
@@ -6016,15 +6032,15 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="42" customHeight="1">
+    <row r="27" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6">
@@ -6038,15 +6054,15 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" ht="40.200000000000003" customHeight="1">
+    <row r="28" spans="1:8" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6">
@@ -6060,15 +6076,15 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" ht="39.6" customHeight="1">
+    <row r="29" spans="1:8" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6">
@@ -6082,7 +6098,7 @@
       </c>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="4" t="s">
         <v>62</v>
@@ -6106,11 +6122,11 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1">
-      <c r="A31" s="125" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="125"/>
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="128" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="128"/>
       <c r="C31" s="2"/>
       <c r="D31" s="5">
         <f>SUM(D30,D23)</f>
@@ -6130,7 +6146,7 @@
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -6140,7 +6156,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -6172,78 +6188,78 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" customWidth="1"/>
     <col min="2" max="2" width="36.88671875" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="131" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="19.2" customHeight="1">
-      <c r="A2" s="137" t="s">
+    <row r="2" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="130"/>
-      <c r="B3" s="131" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="133"/>
+      <c r="B3" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="131" t="s">
+      <c r="C3" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="132" t="s">
+      <c r="D3" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132" t="s">
+      <c r="E3" s="135"/>
+      <c r="F3" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="132"/>
+      <c r="G3" s="135"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="132" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="133"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132" t="s">
+      <c r="E4" s="135"/>
+      <c r="F4" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="132"/>
+      <c r="G4" s="135"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="20.399999999999999">
-      <c r="A5" s="130"/>
-      <c r="B5" s="131"/>
-      <c r="C5" s="131"/>
+    <row r="5" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="133"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
       <c r="D5" s="15" t="s">
         <v>49</v>
       </c>
@@ -6258,7 +6274,7 @@
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -6282,24 +6298,24 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="42.6" customHeight="1">
-      <c r="A7" s="126" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
+    <row r="7" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="129" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="6"/>
@@ -6314,13 +6330,13 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" ht="27" customHeight="1">
+    <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="37"/>
       <c r="B9" s="44" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6">
@@ -6334,13 +6350,13 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="37"/>
       <c r="B10" s="44" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6">
@@ -6354,13 +6370,13 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="37"/>
       <c r="B11" s="44" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6">
@@ -6374,13 +6390,13 @@
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="37"/>
       <c r="B12" s="44" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
@@ -6394,13 +6410,13 @@
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37"/>
       <c r="B13" s="44" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
@@ -6414,13 +6430,13 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="27.6" customHeight="1">
+    <row r="14" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="37"/>
       <c r="B14" s="44" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6">
@@ -6434,13 +6450,13 @@
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="27.6" customHeight="1">
+    <row r="15" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="37"/>
       <c r="B15" s="44" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
@@ -6454,13 +6470,13 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="40.950000000000003" customHeight="1">
+    <row r="16" spans="1:8" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="37"/>
       <c r="B16" s="44" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6">
@@ -6474,15 +6490,15 @@
       </c>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="42" customHeight="1">
+    <row r="17" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="37" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
@@ -6496,12 +6512,12 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="52.2" customHeight="1">
+    <row r="18" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="6"/>
@@ -6516,13 +6532,13 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="37"/>
       <c r="B19" s="44" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6">
@@ -6536,13 +6552,13 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="37"/>
       <c r="B20" s="44" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6">
@@ -6556,13 +6572,13 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="44" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6">
@@ -6576,12 +6592,12 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1">
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C22" s="38"/>
       <c r="D22" s="6"/>
@@ -6596,13 +6612,13 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="37"/>
       <c r="B23" s="44" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6">
@@ -6616,13 +6632,13 @@
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="37"/>
       <c r="B24" s="44" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6">
@@ -6636,13 +6652,13 @@
       </c>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="37"/>
       <c r="B25" s="44" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6">
@@ -6656,13 +6672,13 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="37"/>
       <c r="B26" s="44" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6">
@@ -6676,13 +6692,13 @@
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="27" customHeight="1">
+    <row r="27" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="37"/>
       <c r="B27" s="44" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6">
@@ -6696,15 +6712,15 @@
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" ht="40.200000000000003" customHeight="1">
+    <row r="28" spans="1:8" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6">
@@ -6718,15 +6734,15 @@
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" ht="40.950000000000003" customHeight="1">
+    <row r="29" spans="1:8" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="37" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6">
@@ -6740,7 +6756,7 @@
       </c>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="45" t="s">
         <v>62</v>
@@ -6764,19 +6780,19 @@
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1">
-      <c r="A31" s="127" t="s">
-        <v>245</v>
-      </c>
-      <c r="B31" s="127"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="127"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="127"/>
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="130" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" s="130"/>
+      <c r="C31" s="130"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="130"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -6792,7 +6808,7 @@
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -6808,7 +6824,7 @@
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -6824,7 +6840,7 @@
       </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="19" t="s">
         <v>62</v>
@@ -6848,11 +6864,11 @@
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" ht="25.95" customHeight="1">
-      <c r="A36" s="138" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="138"/>
+    <row r="36" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="141" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="141"/>
       <c r="C36" s="2"/>
       <c r="D36" s="5">
         <f>SUM(D35,D30)</f>
@@ -6872,81 +6888,81 @@
       </c>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" ht="28.95" customHeight="1">
-      <c r="A37" s="136" t="s">
+    <row r="37" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="139"/>
+      <c r="C37" s="139"/>
+      <c r="D37" s="139"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="139"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="136"/>
-      <c r="C37" s="136"/>
-      <c r="D37" s="136"/>
-      <c r="E37" s="136"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="136"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" ht="66" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="E38" s="136" t="s">
         <v>101</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="F38" s="136"/>
+      <c r="G38" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" s="133" t="s">
-        <v>104</v>
-      </c>
-      <c r="F38" s="133"/>
-      <c r="G38" s="17" t="s">
-        <v>105</v>
-      </c>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="134"/>
-      <c r="F39" s="135"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="138"/>
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="134"/>
-      <c r="F40" s="135"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="138"/>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="134"/>
-      <c r="F41" s="135"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="138"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1">
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="135"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="138"/>
       <c r="G42" s="2"/>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -6956,7 +6972,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -6966,7 +6982,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -7003,9 +7019,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" customWidth="1"/>
     <col min="2" max="2" width="36.88671875" customWidth="1"/>
@@ -7013,518 +7029,518 @@
     <col min="4" max="4" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.95" customHeight="1">
-      <c r="A1" s="139" t="s">
+    <row r="1" spans="1:9" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="142" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+    </row>
+    <row r="2" spans="1:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="149" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="149"/>
+      <c r="D2" s="152" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="152"/>
+      <c r="F2" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-    </row>
-    <row r="2" spans="1:9" ht="52.2" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="G2" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="H2" s="153"/>
+      <c r="I2" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="149" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="138"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="143"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="137"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="137"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="137"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="137"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="114"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="114"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="154" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="154"/>
+      <c r="C19" s="154"/>
+      <c r="D19" s="154"/>
+      <c r="E19" s="154"/>
+      <c r="F19" s="154"/>
+      <c r="G19" s="154"/>
+      <c r="H19" s="154"/>
+      <c r="I19" s="154"/>
+    </row>
+    <row r="20" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="156" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="157"/>
+      <c r="D20" s="150" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="151"/>
+      <c r="F20" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="136"/>
+      <c r="I20" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="138"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="137"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="137"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="137"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="137"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="137"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="137"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="137"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="139" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="139"/>
+      <c r="C36" s="139"/>
+      <c r="D36" s="139"/>
+      <c r="E36" s="139"/>
+      <c r="F36" s="139"/>
+      <c r="G36" s="139"/>
+      <c r="H36" s="139"/>
+      <c r="I36" s="139"/>
+    </row>
+    <row r="37" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="155" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="149"/>
-      <c r="F2" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="150" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="150"/>
-      <c r="I2" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="140"/>
-      <c r="E6" s="142"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="142"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="142"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="142"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="142"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="135"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="134"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="142"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="140"/>
-      <c r="E13" s="142"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="134"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="140"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="143"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A17" s="2"/>
-      <c r="B17" s="111"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A18" s="2"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="111"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="36" customHeight="1">
-      <c r="A19" s="151" t="s">
+      <c r="B37" s="155"/>
+      <c r="C37" s="155"/>
+      <c r="D37" s="155"/>
+      <c r="E37" s="155"/>
+      <c r="F37" s="155"/>
+      <c r="G37" s="155"/>
+      <c r="H37" s="155"/>
+      <c r="I37" s="155"/>
+    </row>
+    <row r="38" spans="1:9" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="148" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="151"/>
-      <c r="C19" s="151"/>
-      <c r="D19" s="151"/>
-      <c r="E19" s="151"/>
-      <c r="F19" s="151"/>
-      <c r="G19" s="151"/>
-      <c r="H19" s="151"/>
-      <c r="I19" s="151"/>
-    </row>
-    <row r="20" spans="1:9" ht="54" customHeight="1">
-      <c r="A20" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="153" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="154"/>
-      <c r="D20" s="147" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" s="148"/>
-      <c r="F20" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="133" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A21" s="2"/>
-      <c r="B21" s="134"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A22" s="2"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A23" s="2"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="135"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A24" s="2"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A25" s="2"/>
-      <c r="B25" s="134"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="134"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="135"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A26" s="2"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="135"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A27" s="2"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="135"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A28" s="2"/>
-      <c r="B28" s="134"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="135"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A29" s="2"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="135"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A30" s="2"/>
-      <c r="B30" s="134"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="135"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A31" s="2"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="135"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="135"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A32" s="2"/>
-      <c r="B32" s="134"/>
-      <c r="C32" s="135"/>
-      <c r="D32" s="134"/>
-      <c r="E32" s="135"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="134"/>
-      <c r="H32" s="135"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A33" s="2"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="135"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="135"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="135"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A34" s="2"/>
-      <c r="B34" s="134"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="134"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="134"/>
-      <c r="C35" s="135"/>
-      <c r="D35" s="134"/>
-      <c r="E35" s="135"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="134"/>
-      <c r="H35" s="135"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" ht="24" customHeight="1">
-      <c r="A36" s="136" t="s">
+      <c r="B38" s="148"/>
+      <c r="C38" s="148"/>
+      <c r="D38" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="136"/>
-      <c r="C36" s="136"/>
-      <c r="D36" s="136"/>
-      <c r="E36" s="136"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="136"/>
-      <c r="H36" s="136"/>
-      <c r="I36" s="136"/>
-    </row>
-    <row r="37" spans="1:9" ht="21" customHeight="1">
-      <c r="A37" s="152" t="s">
+      <c r="E38" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="152"/>
-      <c r="C37" s="152"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="152"/>
-      <c r="F37" s="152"/>
-      <c r="G37" s="152"/>
-      <c r="H37" s="152"/>
-      <c r="I37" s="152"/>
-    </row>
-    <row r="38" spans="1:9" ht="35.4" customHeight="1">
-      <c r="A38" s="145" t="s">
+      <c r="F38" s="147"/>
+      <c r="G38" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="145"/>
-      <c r="C38" s="145"/>
-      <c r="D38" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" s="144" t="s">
-        <v>112</v>
-      </c>
-      <c r="F38" s="144"/>
-      <c r="G38" s="110" t="s">
-        <v>113</v>
-      </c>
-      <c r="H38" s="110"/>
-      <c r="I38" s="110"/>
-    </row>
-    <row r="39" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A39" s="143"/>
-      <c r="B39" s="143"/>
-      <c r="C39" s="143"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="113"/>
+    </row>
+    <row r="39" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="146"/>
+      <c r="B39" s="146"/>
+      <c r="C39" s="146"/>
       <c r="D39" s="3"/>
-      <c r="E39" s="143"/>
-      <c r="F39" s="143"/>
-      <c r="G39" s="143"/>
-      <c r="H39" s="143"/>
-      <c r="I39" s="143"/>
-    </row>
-    <row r="40" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A40" s="140"/>
-      <c r="B40" s="141"/>
-      <c r="C40" s="142"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="146"/>
+      <c r="H39" s="146"/>
+      <c r="I39" s="146"/>
+    </row>
+    <row r="40" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="143"/>
+      <c r="B40" s="144"/>
+      <c r="C40" s="145"/>
       <c r="D40" s="3"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="140"/>
-      <c r="H40" s="141"/>
-      <c r="I40" s="142"/>
-    </row>
-    <row r="41" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A41" s="143"/>
-      <c r="B41" s="143"/>
-      <c r="C41" s="143"/>
+      <c r="E40" s="143"/>
+      <c r="F40" s="145"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="144"/>
+      <c r="I40" s="145"/>
+    </row>
+    <row r="41" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="146"/>
+      <c r="B41" s="146"/>
+      <c r="C41" s="146"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="143"/>
-      <c r="F41" s="143"/>
-      <c r="G41" s="143"/>
-      <c r="H41" s="143"/>
-      <c r="I41" s="143"/>
-    </row>
-    <row r="42" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="143"/>
-      <c r="C42" s="143"/>
+      <c r="E41" s="146"/>
+      <c r="F41" s="146"/>
+      <c r="G41" s="146"/>
+      <c r="H41" s="146"/>
+      <c r="I41" s="146"/>
+    </row>
+    <row r="42" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="146"/>
+      <c r="B42" s="146"/>
+      <c r="C42" s="146"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="143"/>
-      <c r="I42" s="143"/>
-    </row>
-    <row r="43" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A43" s="143"/>
-      <c r="B43" s="143"/>
-      <c r="C43" s="143"/>
+      <c r="E42" s="146"/>
+      <c r="F42" s="146"/>
+      <c r="G42" s="146"/>
+      <c r="H42" s="146"/>
+      <c r="I42" s="146"/>
+    </row>
+    <row r="43" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="146"/>
+      <c r="B43" s="146"/>
+      <c r="C43" s="146"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="143"/>
-      <c r="F43" s="143"/>
-      <c r="G43" s="143"/>
-      <c r="H43" s="143"/>
-      <c r="I43" s="143"/>
+      <c r="E43" s="146"/>
+      <c r="F43" s="146"/>
+      <c r="G43" s="146"/>
+      <c r="H43" s="146"/>
+      <c r="I43" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="121">
@@ -7656,9 +7672,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="48" customWidth="1"/>
     <col min="2" max="2" width="7.33203125" style="48" customWidth="1"/>
@@ -7671,418 +7687,410 @@
     <col min="10" max="16384" width="9.109375" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6">
-      <c r="A1" s="155" t="s">
-        <v>283</v>
-      </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-    </row>
-    <row r="2" spans="1:10" ht="20.399999999999999" customHeight="1">
-      <c r="A2" s="80" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="158" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+    </row>
+    <row r="2" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.6">
-      <c r="A3" s="170" t="s">
-        <v>282</v>
-      </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="170"/>
-      <c r="I3" s="170"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.6">
-      <c r="A4" s="172" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="172"/>
-      <c r="C4" s="172"/>
-      <c r="D4" s="172"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="172"/>
-      <c r="G4" s="172"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="58" t="s">
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="173" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="173"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="175" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="177"/>
+      <c r="I4" s="57" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="171"/>
-      <c r="B5" s="171"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="171"/>
-    </row>
-    <row r="6" spans="1:10" ht="29.4" customHeight="1">
-      <c r="A6" s="162" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="174"/>
+      <c r="B5" s="174"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="174"/>
+    </row>
+    <row r="6" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="165" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="162"/>
-      <c r="C6" s="162"/>
-      <c r="D6" s="162"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="59" t="s">
+      <c r="B6" s="165"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="60" t="s">
+      <c r="I6" s="59" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.6">
-      <c r="A7" s="167" t="s">
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="170" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="167"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.6">
-      <c r="A8" s="167" t="s">
+      <c r="B7" s="170"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="170"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="68"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="170" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="167"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="60" t="s">
+      <c r="B8" s="170"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="170"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="69"/>
+    </row>
+    <row r="9" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="171" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="171"/>
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="70"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="170" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="170"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="64"/>
+    </row>
+    <row r="11" spans="1:10" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="172" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="172"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="172"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="176"/>
+      <c r="B12" s="176"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+    </row>
+    <row r="13" spans="1:10" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="168" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A9" s="168" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="168"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="62" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.6">
-      <c r="A10" s="167" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="167"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="63">
-        <f>G11-G7</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="69"/>
-    </row>
-    <row r="11" spans="1:10" ht="23.4" customHeight="1">
-      <c r="A11" s="169" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="169"/>
-      <c r="C11" s="169"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="169"/>
-      <c r="F11" s="169"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="63" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="41.4" customHeight="1">
-      <c r="A12" s="173"/>
-      <c r="B12" s="173"/>
-      <c r="C12" s="173"/>
-      <c r="D12" s="173"/>
-      <c r="E12" s="173"/>
-      <c r="F12" s="173"/>
-      <c r="G12" s="173"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="173"/>
-    </row>
-    <row r="13" spans="1:10" ht="31.95" customHeight="1">
-      <c r="A13" s="165" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="166"/>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-    </row>
-    <row r="14" spans="1:10" ht="29.4" customHeight="1">
-      <c r="A14" s="164" t="s">
+      <c r="B13" s="169"/>
+      <c r="C13" s="169"/>
+      <c r="D13" s="169"/>
+      <c r="E13" s="169"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="169"/>
+      <c r="I13" s="169"/>
+    </row>
+    <row r="14" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="164"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="164"/>
-      <c r="E14" s="164"/>
-      <c r="F14" s="164"/>
-      <c r="G14" s="163" t="s">
+      <c r="B14" s="167"/>
+      <c r="C14" s="167"/>
+      <c r="D14" s="167"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="166" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="164"/>
-      <c r="I14" s="164"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A15" s="158"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="158"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="158"/>
-      <c r="I15" s="158"/>
-    </row>
-    <row r="16" spans="1:10" ht="19.95" customHeight="1">
-      <c r="A16" s="158"/>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="158"/>
-      <c r="I16" s="158"/>
-    </row>
-    <row r="17" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A17" s="158"/>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
-      <c r="F17" s="158"/>
-      <c r="G17" s="158"/>
-      <c r="H17" s="158"/>
-      <c r="I17" s="158"/>
-    </row>
-    <row r="18" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A18" s="158"/>
-      <c r="B18" s="158"/>
-      <c r="C18" s="158"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="158"/>
-      <c r="I18" s="158"/>
-    </row>
-    <row r="19" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A19" s="158"/>
-      <c r="B19" s="158"/>
-      <c r="C19" s="158"/>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
-      <c r="F19" s="158"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="158"/>
-      <c r="I19" s="158"/>
-    </row>
-    <row r="20" spans="1:9" ht="33.6" customHeight="1">
-      <c r="A20" s="160" t="s">
+      <c r="H14" s="167"/>
+      <c r="I14" s="167"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="161"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="161"/>
+      <c r="G15" s="161"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+    </row>
+    <row r="16" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="161"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="161"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="161"/>
+    </row>
+    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="161"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="161"/>
+      <c r="D17" s="161"/>
+      <c r="E17" s="161"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="161"/>
+    </row>
+    <row r="18" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="161"/>
+      <c r="B18" s="161"/>
+      <c r="C18" s="161"/>
+      <c r="D18" s="161"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="161"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="161"/>
+    </row>
+    <row r="19" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="161"/>
+      <c r="B19" s="161"/>
+      <c r="C19" s="161"/>
+      <c r="D19" s="161"/>
+      <c r="E19" s="161"/>
+      <c r="F19" s="161"/>
+      <c r="G19" s="161"/>
+      <c r="H19" s="161"/>
+      <c r="I19" s="161"/>
+    </row>
+    <row r="20" spans="1:9" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="163" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="161"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="161"/>
-      <c r="E20" s="161"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="161"/>
-      <c r="H20" s="161"/>
-      <c r="I20" s="161"/>
-    </row>
-    <row r="21" spans="1:9" ht="21" customHeight="1">
-      <c r="A21" s="65" t="s">
+      <c r="B20" s="164"/>
+      <c r="C20" s="164"/>
+      <c r="D20" s="164"/>
+      <c r="E20" s="164"/>
+      <c r="F20" s="164"/>
+      <c r="G20" s="164"/>
+      <c r="H20" s="164"/>
+      <c r="I20" s="164"/>
+    </row>
+    <row r="21" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="162" t="s">
+      <c r="B21" s="165" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="162"/>
-      <c r="D21" s="162"/>
-      <c r="E21" s="162"/>
-      <c r="F21" s="162"/>
-      <c r="G21" s="162"/>
-      <c r="H21" s="162"/>
-      <c r="I21" s="162"/>
-    </row>
-    <row r="22" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A22" s="66"/>
-      <c r="B22" s="158"/>
-      <c r="C22" s="158"/>
-      <c r="D22" s="158"/>
-      <c r="E22" s="158"/>
-      <c r="F22" s="158"/>
-      <c r="G22" s="158"/>
-      <c r="H22" s="158"/>
-      <c r="I22" s="158"/>
-    </row>
-    <row r="23" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A23" s="66"/>
-      <c r="B23" s="158"/>
-      <c r="C23" s="158"/>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="158"/>
-      <c r="I23" s="158"/>
-    </row>
-    <row r="24" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A24" s="66"/>
-      <c r="B24" s="158"/>
-      <c r="C24" s="158"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
-    </row>
-    <row r="25" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A25" s="66"/>
-      <c r="B25" s="158"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
-    </row>
-    <row r="26" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A26" s="66"/>
-      <c r="B26" s="158"/>
-      <c r="C26" s="158"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="158"/>
-      <c r="G26" s="158"/>
-      <c r="H26" s="158"/>
-      <c r="I26" s="158"/>
-    </row>
-    <row r="27" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A27" s="66"/>
-      <c r="B27" s="158"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="158"/>
-      <c r="G27" s="158"/>
-      <c r="H27" s="158"/>
-      <c r="I27" s="158"/>
-    </row>
-    <row r="28" spans="1:9" ht="16.95" customHeight="1">
-      <c r="A28" s="66"/>
-      <c r="B28" s="158"/>
-      <c r="C28" s="158"/>
-      <c r="D28" s="158"/>
-      <c r="E28" s="158"/>
-      <c r="F28" s="158"/>
-      <c r="G28" s="158"/>
-      <c r="H28" s="158"/>
-      <c r="I28" s="158"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="159"/>
-      <c r="B29" s="159"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="159"/>
-      <c r="H29" s="159"/>
-      <c r="I29" s="159"/>
-    </row>
-    <row r="30" spans="1:9" ht="60" customHeight="1">
-      <c r="A30" s="156" t="s">
+      <c r="C21" s="165"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
+      <c r="H21" s="165"/>
+      <c r="I21" s="165"/>
+    </row>
+    <row r="22" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="61"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="161"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
+    </row>
+    <row r="23" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="61"/>
+      <c r="B23" s="161"/>
+      <c r="C23" s="161"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="161"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="161"/>
+    </row>
+    <row r="24" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="61"/>
+      <c r="B24" s="161"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="161"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="161"/>
+    </row>
+    <row r="25" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="61"/>
+      <c r="B25" s="161"/>
+      <c r="C25" s="161"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="161"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="161"/>
+    </row>
+    <row r="26" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="61"/>
+      <c r="B26" s="161"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="161"/>
+      <c r="E26" s="161"/>
+      <c r="F26" s="161"/>
+      <c r="G26" s="161"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="161"/>
+    </row>
+    <row r="27" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="61"/>
+      <c r="B27" s="161"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="161"/>
+      <c r="E27" s="161"/>
+      <c r="F27" s="161"/>
+      <c r="G27" s="161"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="161"/>
+    </row>
+    <row r="28" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="61"/>
+      <c r="B28" s="161"/>
+      <c r="C28" s="161"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="161"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="161"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="162"/>
+      <c r="B29" s="162"/>
+      <c r="C29" s="162"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="162"/>
+    </row>
+    <row r="30" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="159" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="156"/>
-      <c r="C30" s="156"/>
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156" t="s">
-        <v>279</v>
-      </c>
-      <c r="G30" s="156"/>
-      <c r="H30" s="156"/>
-      <c r="I30" s="67"/>
-    </row>
-    <row r="31" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A31" s="157" t="s">
+      <c r="B30" s="159"/>
+      <c r="C30" s="159"/>
+      <c r="D30" s="159"/>
+      <c r="E30" s="159"/>
+      <c r="F30" s="159" t="s">
+        <v>276</v>
+      </c>
+      <c r="G30" s="159"/>
+      <c r="H30" s="159"/>
+      <c r="I30" s="62"/>
+    </row>
+    <row r="31" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="157"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="157" t="s">
-        <v>267</v>
-      </c>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="68"/>
-    </row>
-    <row r="32" spans="1:9" ht="19.95" customHeight="1">
-      <c r="A32" s="156" t="s">
+      <c r="B31" s="160"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="160"/>
+      <c r="E31" s="160"/>
+      <c r="F31" s="160" t="s">
+        <v>264</v>
+      </c>
+      <c r="G31" s="160"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="63"/>
+    </row>
+    <row r="32" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="156"/>
-      <c r="C32" s="156"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="157" t="s">
+      <c r="B32" s="159"/>
+      <c r="C32" s="159"/>
+      <c r="D32" s="159"/>
+      <c r="E32" s="159"/>
+      <c r="F32" s="160" t="s">
         <v>81</v>
       </c>
-      <c r="G32" s="157"/>
-      <c r="H32" s="157"/>
-      <c r="I32" s="67"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="41">
